--- a/meta/plainApi/BlancoApiPlainSample.xlsx
+++ b/meta/plainApi/BlancoApiPlainSample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tueda/data/webstorm/blanco/blancoRestGeneratorKt/meta/plainApi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EC7C8AC-B75F-9845-B850-9A2307008072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B033B0-62E8-DF4D-9FF3-E495F7DCFE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="4400" windowWidth="29440" windowHeight="20500" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="262">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
@@ -2619,6 +2619,26 @@
   </si>
   <si>
     <t>※ 当面の間 kotlin のみ対応</t>
+    <rPh sb="2" eb="4">
+      <t xml:space="preserve">トウメｎ </t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t xml:space="preserve">アイダ </t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t xml:space="preserve">タイオウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>仮想パラメータ</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">カソウパラメータ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※ このクラスで使用されている仮想パラメータ（カンマ区切り、TypeReference作成用）</t>
     <rPh sb="2" eb="4">
       <t xml:space="preserve">トウメｎ </t>
     </rPh>
@@ -3816,19 +3836,133 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3843,136 +3977,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3982,8 +3990,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3994,8 +4014,8 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4585,152 +4605,152 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="133" t="s">
+      <c r="A5" s="169" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="177" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="140"/>
-      <c r="C6" s="141"/>
-      <c r="D6" s="134" t="s">
+      <c r="B6" s="178"/>
+      <c r="C6" s="179"/>
+      <c r="D6" s="175" t="s">
         <v>233</v>
       </c>
-      <c r="E6" s="134"/>
+      <c r="E6" s="175"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="169" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="134" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="175" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="134"/>
+      <c r="E7" s="175"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="169" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="134" t="s">
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="175" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="134"/>
+      <c r="E8" s="175"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="169" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="134" t="s">
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="175" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="134"/>
+      <c r="E9" s="175"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="133" t="s">
+      <c r="A10" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="175"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="133" t="s">
+      <c r="A11" s="169" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="134" t="s">
+      <c r="B11" s="169"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="175" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="134"/>
+      <c r="E11" s="175"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="135" t="s">
+      <c r="A12" s="145" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="135"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="137" t="s">
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="E12" s="137"/>
+      <c r="E12" s="158"/>
       <c r="F12" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="135" t="s">
+      <c r="A13" s="145" t="s">
         <v>170</v>
       </c>
-      <c r="B13" s="135"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="136" t="s">
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="157" t="s">
         <v>208</v>
       </c>
-      <c r="E13" s="137"/>
+      <c r="E13" s="158"/>
     </row>
     <row r="14" spans="1:6" ht="55" customHeight="1">
-      <c r="A14" s="135" t="s">
+      <c r="A14" s="145" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="135"/>
-      <c r="C14" s="135"/>
-      <c r="D14" s="138" t="s">
+      <c r="B14" s="145"/>
+      <c r="C14" s="145"/>
+      <c r="D14" s="176" t="s">
         <v>232</v>
       </c>
-      <c r="E14" s="137"/>
+      <c r="E14" s="158"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="145" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="135"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="137"/>
+      <c r="B15" s="145"/>
+      <c r="C15" s="145"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="158"/>
       <c r="F15" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="135" t="s">
+      <c r="A16" s="145" t="s">
         <v>192</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="135"/>
-      <c r="D16" s="136"/>
-      <c r="E16" s="137"/>
+      <c r="B16" s="145"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="158"/>
       <c r="F16" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="177" t="s">
+      <c r="A17" s="159" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="178"/>
-      <c r="C17" s="179"/>
+      <c r="B17" s="160"/>
+      <c r="C17" s="161"/>
       <c r="D17" s="104"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="164" t="s">
+      <c r="A18" s="146" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="165"/>
-      <c r="C18" s="166"/>
+      <c r="B18" s="147"/>
+      <c r="C18" s="148"/>
       <c r="D18" s="90" t="s">
         <v>137</v>
       </c>
@@ -4750,15 +4770,15 @@
       <c r="B19" s="6"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="174" t="s">
+      <c r="A20" s="154" t="s">
         <v>181</v>
       </c>
-      <c r="B20" s="175"/>
-      <c r="C20" s="175"/>
-      <c r="D20" s="175"/>
-      <c r="E20" s="175"/>
-      <c r="F20" s="175"/>
-      <c r="G20" s="176"/>
+      <c r="B20" s="155"/>
+      <c r="C20" s="155"/>
+      <c r="D20" s="155"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="155"/>
+      <c r="G20" s="156"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="91" t="s">
@@ -4802,28 +4822,28 @@
       <c r="C24"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="173" t="s">
+      <c r="A25" s="133" t="s">
         <v>182</v>
       </c>
-      <c r="B25" s="173"/>
-      <c r="C25" s="173"/>
-      <c r="D25" s="173"/>
-      <c r="E25" s="173"/>
-      <c r="F25" s="173"/>
-      <c r="G25" s="173"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="167" t="s">
+      <c r="B26" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="168"/>
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="169"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="136"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="95"/>
@@ -4834,12 +4854,12 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="106"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
+      <c r="B27" s="164"/>
+      <c r="C27" s="164"/>
+      <c r="D27" s="164"/>
+      <c r="E27" s="164"/>
+      <c r="F27" s="164"/>
+      <c r="G27" s="164"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -4850,12 +4870,12 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="107"/>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="154"/>
-      <c r="E28" s="154"/>
-      <c r="F28" s="154"/>
-      <c r="G28" s="154"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="165"/>
+      <c r="E28" s="165"/>
+      <c r="F28" s="165"/>
+      <c r="G28" s="165"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -4866,12 +4886,12 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="108"/>
-      <c r="B29" s="156"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="156"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="156"/>
-      <c r="G29" s="156"/>
+      <c r="B29" s="166"/>
+      <c r="C29" s="166"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="166"/>
+      <c r="F29" s="166"/>
+      <c r="G29" s="166"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="102"/>
@@ -4903,28 +4923,28 @@
       <c r="C31"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="173" t="s">
+      <c r="A32" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="173"/>
-      <c r="C32" s="173"/>
-      <c r="D32" s="173"/>
-      <c r="E32" s="173"/>
-      <c r="F32" s="173"/>
-      <c r="G32" s="173"/>
+      <c r="B32" s="133"/>
+      <c r="C32" s="133"/>
+      <c r="D32" s="133"/>
+      <c r="E32" s="133"/>
+      <c r="F32" s="133"/>
+      <c r="G32" s="133"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="167" t="s">
+      <c r="B33" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="168"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="169"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="136"/>
       <c r="H33" s="95"/>
       <c r="I33" s="95"/>
       <c r="J33" s="95"/>
@@ -4937,14 +4957,14 @@
       <c r="A34" s="106">
         <v>1</v>
       </c>
-      <c r="B34" s="149" t="s">
+      <c r="B34" s="137" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="149"/>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
-      <c r="G34" s="149"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -4955,12 +4975,12 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="107"/>
-      <c r="B35" s="150"/>
-      <c r="C35" s="150"/>
-      <c r="D35" s="150"/>
-      <c r="E35" s="150"/>
-      <c r="F35" s="150"/>
-      <c r="G35" s="150"/>
+      <c r="B35" s="138"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="102"/>
@@ -4971,12 +4991,12 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="108"/>
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
+      <c r="B36" s="139"/>
+      <c r="C36" s="139"/>
+      <c r="D36" s="139"/>
+      <c r="E36" s="139"/>
+      <c r="F36" s="139"/>
+      <c r="G36" s="139"/>
       <c r="H36" s="102"/>
       <c r="I36" s="102"/>
       <c r="J36" s="102"/>
@@ -4989,28 +5009,28 @@
       <c r="C37"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="170" t="s">
+      <c r="A38" s="151" t="s">
         <v>183</v>
       </c>
-      <c r="B38" s="171"/>
-      <c r="C38" s="171"/>
-      <c r="D38" s="171"/>
-      <c r="E38" s="171"/>
-      <c r="F38" s="171"/>
-      <c r="G38" s="172"/>
+      <c r="B38" s="152"/>
+      <c r="C38" s="152"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
+      <c r="F38" s="152"/>
+      <c r="G38" s="153"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="148" t="s">
+      <c r="B39" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C39" s="148"/>
-      <c r="D39" s="148"/>
-      <c r="E39" s="148"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="148"/>
+      <c r="C39" s="171"/>
+      <c r="D39" s="171"/>
+      <c r="E39" s="171"/>
+      <c r="F39" s="171"/>
+      <c r="G39" s="171"/>
       <c r="H39" s="95"/>
       <c r="I39" s="95"/>
       <c r="J39" s="95"/>
@@ -5023,14 +5043,14 @@
       <c r="A40" s="106">
         <v>1</v>
       </c>
-      <c r="B40" s="149" t="s">
+      <c r="B40" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C40" s="149"/>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="149"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -5041,12 +5061,12 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="107"/>
-      <c r="B41" s="150"/>
-      <c r="C41" s="150"/>
-      <c r="D41" s="150"/>
-      <c r="E41" s="150"/>
-      <c r="F41" s="150"/>
-      <c r="G41" s="150"/>
+      <c r="B41" s="138"/>
+      <c r="C41" s="138"/>
+      <c r="D41" s="138"/>
+      <c r="E41" s="138"/>
+      <c r="F41" s="138"/>
+      <c r="G41" s="138"/>
       <c r="H41" s="102"/>
       <c r="I41" s="102"/>
       <c r="J41" s="102"/>
@@ -5057,12 +5077,12 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="108"/>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="151"/>
-      <c r="E42" s="151"/>
-      <c r="F42" s="151"/>
-      <c r="G42" s="151"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="139"/>
+      <c r="D42" s="139"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
       <c r="H42" s="102"/>
       <c r="I42" s="102"/>
       <c r="J42" s="102"/>
@@ -5087,28 +5107,28 @@
       <c r="M43"/>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="170" t="s">
+      <c r="A44" s="151" t="s">
         <v>184</v>
       </c>
-      <c r="B44" s="171"/>
-      <c r="C44" s="171"/>
-      <c r="D44" s="171"/>
-      <c r="E44" s="171"/>
-      <c r="F44" s="171"/>
-      <c r="G44" s="172"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="152"/>
+      <c r="E44" s="152"/>
+      <c r="F44" s="152"/>
+      <c r="G44" s="153"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="148" t="s">
+      <c r="B45" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C45" s="148"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="148"/>
-      <c r="F45" s="148"/>
-      <c r="G45" s="148"/>
+      <c r="C45" s="171"/>
+      <c r="D45" s="171"/>
+      <c r="E45" s="171"/>
+      <c r="F45" s="171"/>
+      <c r="G45" s="171"/>
       <c r="H45" s="95"/>
       <c r="I45" s="95"/>
       <c r="J45" s="95"/>
@@ -5119,12 +5139,12 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="106"/>
-      <c r="B46" s="152"/>
-      <c r="C46" s="152"/>
-      <c r="D46" s="152"/>
-      <c r="E46" s="152"/>
-      <c r="F46" s="152"/>
-      <c r="G46" s="153"/>
+      <c r="B46" s="164"/>
+      <c r="C46" s="164"/>
+      <c r="D46" s="164"/>
+      <c r="E46" s="164"/>
+      <c r="F46" s="164"/>
+      <c r="G46" s="172"/>
       <c r="H46" s="102"/>
       <c r="I46" s="102"/>
       <c r="J46" s="102"/>
@@ -5135,12 +5155,12 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="107"/>
-      <c r="B47" s="154"/>
-      <c r="C47" s="154"/>
-      <c r="D47" s="154"/>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="155"/>
+      <c r="B47" s="165"/>
+      <c r="C47" s="165"/>
+      <c r="D47" s="165"/>
+      <c r="E47" s="165"/>
+      <c r="F47" s="165"/>
+      <c r="G47" s="173"/>
       <c r="H47" s="102"/>
       <c r="I47" s="102"/>
       <c r="J47" s="102"/>
@@ -5151,12 +5171,12 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="108"/>
-      <c r="B48" s="156"/>
-      <c r="C48" s="156"/>
-      <c r="D48" s="156"/>
-      <c r="E48" s="156"/>
-      <c r="F48" s="156"/>
-      <c r="G48" s="157"/>
+      <c r="B48" s="166"/>
+      <c r="C48" s="166"/>
+      <c r="D48" s="166"/>
+      <c r="E48" s="166"/>
+      <c r="F48" s="166"/>
+      <c r="G48" s="174"/>
       <c r="H48" s="102"/>
       <c r="I48" s="102"/>
       <c r="J48" s="102"/>
@@ -5182,15 +5202,15 @@
       <c r="O49"/>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" s="173" t="s">
+      <c r="A50" s="133" t="s">
         <v>204</v>
       </c>
-      <c r="B50" s="173"/>
-      <c r="C50" s="173"/>
-      <c r="D50" s="173"/>
-      <c r="E50" s="173"/>
-      <c r="F50" s="173"/>
-      <c r="G50" s="173"/>
+      <c r="B50" s="133"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="133"/>
+      <c r="E50" s="133"/>
+      <c r="F50" s="133"/>
+      <c r="G50" s="133"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51" s="105" t="s">
@@ -5306,236 +5326,289 @@
       <c r="F56" s="5"/>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="161" t="s">
+      <c r="A57" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="163"/>
-      <c r="C57" s="161" t="s">
+      <c r="B57" s="144"/>
+      <c r="C57" s="142" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="162"/>
-      <c r="E57" s="163"/>
+      <c r="D57" s="143"/>
+      <c r="E57" s="144"/>
       <c r="F57" s="27" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" s="158"/>
-      <c r="B58" s="160"/>
-      <c r="C58" s="158"/>
-      <c r="D58" s="159"/>
-      <c r="E58" s="160"/>
+      <c r="A58" s="149"/>
+      <c r="B58" s="150"/>
+      <c r="C58" s="149"/>
+      <c r="D58" s="167"/>
+      <c r="E58" s="150"/>
       <c r="F58" s="43"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="142"/>
-      <c r="B59" s="144"/>
-      <c r="C59" s="142"/>
-      <c r="D59" s="143"/>
-      <c r="E59" s="144"/>
+      <c r="A59" s="140"/>
+      <c r="B59" s="141"/>
+      <c r="C59" s="140"/>
+      <c r="D59" s="168"/>
+      <c r="E59" s="141"/>
       <c r="F59" s="43"/>
     </row>
     <row r="60" spans="1:15">
-      <c r="A60" s="142"/>
-      <c r="B60" s="144"/>
-      <c r="C60" s="142"/>
-      <c r="D60" s="143"/>
-      <c r="E60" s="144"/>
+      <c r="A60" s="140"/>
+      <c r="B60" s="141"/>
+      <c r="C60" s="140"/>
+      <c r="D60" s="168"/>
+      <c r="E60" s="141"/>
       <c r="F60" s="43"/>
     </row>
     <row r="61" spans="1:15">
-      <c r="A61" s="142"/>
-      <c r="B61" s="144"/>
-      <c r="C61" s="142"/>
-      <c r="D61" s="143"/>
-      <c r="E61" s="144"/>
+      <c r="A61" s="140"/>
+      <c r="B61" s="141"/>
+      <c r="C61" s="140"/>
+      <c r="D61" s="168"/>
+      <c r="E61" s="141"/>
       <c r="F61" s="43"/>
     </row>
     <row r="62" spans="1:15">
-      <c r="A62" s="142"/>
-      <c r="B62" s="144"/>
-      <c r="C62" s="142"/>
-      <c r="D62" s="143"/>
-      <c r="E62" s="144"/>
+      <c r="A62" s="140"/>
+      <c r="B62" s="141"/>
+      <c r="C62" s="140"/>
+      <c r="D62" s="168"/>
+      <c r="E62" s="141"/>
       <c r="F62" s="43"/>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" s="142"/>
-      <c r="B63" s="144"/>
-      <c r="C63" s="142"/>
-      <c r="D63" s="143"/>
-      <c r="E63" s="144"/>
+      <c r="A63" s="140"/>
+      <c r="B63" s="141"/>
+      <c r="C63" s="140"/>
+      <c r="D63" s="168"/>
+      <c r="E63" s="141"/>
       <c r="F63" s="43"/>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" s="142"/>
-      <c r="B64" s="144"/>
-      <c r="C64" s="142"/>
-      <c r="D64" s="143"/>
-      <c r="E64" s="144"/>
+      <c r="A64" s="140"/>
+      <c r="B64" s="141"/>
+      <c r="C64" s="140"/>
+      <c r="D64" s="168"/>
+      <c r="E64" s="141"/>
       <c r="F64" s="43"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="142"/>
-      <c r="B65" s="144"/>
-      <c r="C65" s="142"/>
-      <c r="D65" s="143"/>
-      <c r="E65" s="144"/>
+      <c r="A65" s="140"/>
+      <c r="B65" s="141"/>
+      <c r="C65" s="140"/>
+      <c r="D65" s="168"/>
+      <c r="E65" s="141"/>
       <c r="F65" s="43"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="142"/>
-      <c r="B66" s="144"/>
-      <c r="C66" s="142"/>
-      <c r="D66" s="143"/>
-      <c r="E66" s="144"/>
+      <c r="A66" s="140"/>
+      <c r="B66" s="141"/>
+      <c r="C66" s="140"/>
+      <c r="D66" s="168"/>
+      <c r="E66" s="141"/>
       <c r="F66" s="43"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="142"/>
-      <c r="B67" s="144"/>
-      <c r="C67" s="142"/>
-      <c r="D67" s="143"/>
-      <c r="E67" s="144"/>
+      <c r="A67" s="140"/>
+      <c r="B67" s="141"/>
+      <c r="C67" s="140"/>
+      <c r="D67" s="168"/>
+      <c r="E67" s="141"/>
       <c r="F67" s="43"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="142"/>
-      <c r="B68" s="144"/>
-      <c r="C68" s="142"/>
-      <c r="D68" s="143"/>
-      <c r="E68" s="144"/>
+      <c r="A68" s="140"/>
+      <c r="B68" s="141"/>
+      <c r="C68" s="140"/>
+      <c r="D68" s="168"/>
+      <c r="E68" s="141"/>
       <c r="F68" s="43"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="142"/>
-      <c r="B69" s="144"/>
-      <c r="C69" s="142"/>
-      <c r="D69" s="143"/>
-      <c r="E69" s="144"/>
+      <c r="A69" s="140"/>
+      <c r="B69" s="141"/>
+      <c r="C69" s="140"/>
+      <c r="D69" s="168"/>
+      <c r="E69" s="141"/>
       <c r="F69" s="43"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="142"/>
-      <c r="B70" s="144"/>
-      <c r="C70" s="142"/>
-      <c r="D70" s="143"/>
-      <c r="E70" s="144"/>
+      <c r="A70" s="140"/>
+      <c r="B70" s="141"/>
+      <c r="C70" s="140"/>
+      <c r="D70" s="168"/>
+      <c r="E70" s="141"/>
       <c r="F70" s="43"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="142"/>
-      <c r="B71" s="144"/>
-      <c r="C71" s="142"/>
-      <c r="D71" s="143"/>
-      <c r="E71" s="144"/>
+      <c r="A71" s="140"/>
+      <c r="B71" s="141"/>
+      <c r="C71" s="140"/>
+      <c r="D71" s="168"/>
+      <c r="E71" s="141"/>
       <c r="F71" s="43"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="142"/>
-      <c r="B72" s="144"/>
-      <c r="C72" s="142"/>
-      <c r="D72" s="143"/>
-      <c r="E72" s="144"/>
+      <c r="A72" s="140"/>
+      <c r="B72" s="141"/>
+      <c r="C72" s="140"/>
+      <c r="D72" s="168"/>
+      <c r="E72" s="141"/>
       <c r="F72" s="43"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="142"/>
-      <c r="B73" s="144"/>
-      <c r="C73" s="142"/>
-      <c r="D73" s="143"/>
-      <c r="E73" s="144"/>
+      <c r="A73" s="140"/>
+      <c r="B73" s="141"/>
+      <c r="C73" s="140"/>
+      <c r="D73" s="168"/>
+      <c r="E73" s="141"/>
       <c r="F73" s="43"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="142"/>
-      <c r="B74" s="144"/>
-      <c r="C74" s="142"/>
-      <c r="D74" s="143"/>
-      <c r="E74" s="144"/>
+      <c r="A74" s="140"/>
+      <c r="B74" s="141"/>
+      <c r="C74" s="140"/>
+      <c r="D74" s="168"/>
+      <c r="E74" s="141"/>
       <c r="F74" s="43"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="142"/>
-      <c r="B75" s="144"/>
-      <c r="C75" s="142"/>
-      <c r="D75" s="143"/>
-      <c r="E75" s="144"/>
+      <c r="A75" s="140"/>
+      <c r="B75" s="141"/>
+      <c r="C75" s="140"/>
+      <c r="D75" s="168"/>
+      <c r="E75" s="141"/>
       <c r="F75" s="43"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="142"/>
-      <c r="B76" s="144"/>
-      <c r="C76" s="142"/>
-      <c r="D76" s="143"/>
-      <c r="E76" s="144"/>
+      <c r="A76" s="140"/>
+      <c r="B76" s="141"/>
+      <c r="C76" s="140"/>
+      <c r="D76" s="168"/>
+      <c r="E76" s="141"/>
       <c r="F76" s="43"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="142"/>
-      <c r="B77" s="144"/>
-      <c r="C77" s="142"/>
-      <c r="D77" s="143"/>
-      <c r="E77" s="144"/>
+      <c r="A77" s="140"/>
+      <c r="B77" s="141"/>
+      <c r="C77" s="140"/>
+      <c r="D77" s="168"/>
+      <c r="E77" s="141"/>
       <c r="F77" s="43"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="142"/>
-      <c r="B78" s="144"/>
-      <c r="C78" s="142"/>
-      <c r="D78" s="143"/>
-      <c r="E78" s="144"/>
+      <c r="A78" s="140"/>
+      <c r="B78" s="141"/>
+      <c r="C78" s="140"/>
+      <c r="D78" s="168"/>
+      <c r="E78" s="141"/>
       <c r="F78" s="43"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="142"/>
-      <c r="B79" s="144"/>
-      <c r="C79" s="142"/>
-      <c r="D79" s="143"/>
-      <c r="E79" s="144"/>
+      <c r="A79" s="140"/>
+      <c r="B79" s="141"/>
+      <c r="C79" s="140"/>
+      <c r="D79" s="168"/>
+      <c r="E79" s="141"/>
       <c r="F79" s="43"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="142"/>
-      <c r="B80" s="144"/>
-      <c r="C80" s="142"/>
-      <c r="D80" s="143"/>
-      <c r="E80" s="144"/>
+      <c r="A80" s="140"/>
+      <c r="B80" s="141"/>
+      <c r="C80" s="140"/>
+      <c r="D80" s="168"/>
+      <c r="E80" s="141"/>
       <c r="F80" s="43"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="142"/>
-      <c r="B81" s="144"/>
-      <c r="C81" s="142"/>
-      <c r="D81" s="143"/>
-      <c r="E81" s="144"/>
+      <c r="A81" s="140"/>
+      <c r="B81" s="141"/>
+      <c r="C81" s="140"/>
+      <c r="D81" s="168"/>
+      <c r="E81" s="141"/>
       <c r="F81" s="43"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="145"/>
-      <c r="B82" s="147"/>
-      <c r="C82" s="145"/>
-      <c r="D82" s="146"/>
-      <c r="E82" s="147"/>
+      <c r="A82" s="162"/>
+      <c r="B82" s="163"/>
+      <c r="C82" s="162"/>
+      <c r="D82" s="170"/>
+      <c r="E82" s="163"/>
       <c r="F82" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B48:G48"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="C57:E57"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A18:C18"/>
@@ -5552,74 +5625,21 @@
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B47:G47"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
@@ -5826,10 +5846,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="137"/>
+      <c r="D17" s="158"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -5839,20 +5859,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="137" t="s">
+      <c r="C18" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="137"/>
+      <c r="D18" s="158"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="157" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="137"/>
+      <c r="D19" s="158"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="112" t="s">
@@ -5933,28 +5953,28 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="173" t="s">
+      <c r="A24" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="173"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="173"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="167" t="s">
+      <c r="B25" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="168"/>
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="169"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136"/>
       <c r="H25" s="95"/>
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
@@ -5971,12 +5991,12 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="106"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
+      <c r="B26" s="164"/>
+      <c r="C26" s="164"/>
+      <c r="D26" s="164"/>
+      <c r="E26" s="164"/>
+      <c r="F26" s="164"/>
+      <c r="G26" s="164"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="J26" s="102"/>
@@ -5993,12 +6013,12 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="107"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="154"/>
-      <c r="G27" s="154"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="165"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="165"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -6015,12 +6035,12 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="108"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="156"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
-      <c r="F28" s="156"/>
-      <c r="G28" s="156"/>
+      <c r="B28" s="166"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="166"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -6039,28 +6059,28 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="170" t="s">
+      <c r="A30" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="171"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="172"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="152"/>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="153"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="148" t="s">
+      <c r="B31" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
+      <c r="C31" s="171"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="171"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="171"/>
       <c r="H31" s="95"/>
       <c r="I31" s="95"/>
       <c r="J31" s="95"/>
@@ -6079,14 +6099,14 @@
       <c r="A32" s="106">
         <v>1</v>
       </c>
-      <c r="B32" s="149" t="s">
+      <c r="B32" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="149"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -6103,12 +6123,12 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="107"/>
-      <c r="B33" s="150"/>
-      <c r="C33" s="150"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="150"/>
-      <c r="G33" s="150"/>
+      <c r="B33" s="138"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -6125,12 +6145,12 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="108"/>
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="151"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -6167,28 +6187,28 @@
       <c r="S35"/>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="170" t="s">
+      <c r="A36" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="171"/>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="172"/>
+      <c r="B36" s="152"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="153"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="148" t="s">
+      <c r="B37" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="148"/>
-      <c r="D37" s="148"/>
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
+      <c r="C37" s="171"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="171"/>
+      <c r="F37" s="171"/>
+      <c r="G37" s="171"/>
       <c r="H37" s="95"/>
       <c r="I37" s="95"/>
       <c r="J37" s="95"/>
@@ -6205,12 +6225,12 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="106"/>
-      <c r="B38" s="152"/>
-      <c r="C38" s="152"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="153"/>
+      <c r="B38" s="164"/>
+      <c r="C38" s="164"/>
+      <c r="D38" s="164"/>
+      <c r="E38" s="164"/>
+      <c r="F38" s="164"/>
+      <c r="G38" s="172"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -6227,12 +6247,12 @@
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="107"/>
-      <c r="B39" s="154"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="154"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
+      <c r="B39" s="165"/>
+      <c r="C39" s="165"/>
+      <c r="D39" s="165"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="165"/>
+      <c r="G39" s="173"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -6249,12 +6269,12 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="108"/>
-      <c r="B40" s="156"/>
-      <c r="C40" s="156"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="157"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="166"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="174"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -6327,16 +6347,16 @@
       <c r="B44" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="186" t="s">
+      <c r="C44" s="182" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="184" t="s">
+      <c r="E44" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F44" s="184" t="s">
+      <c r="F44" s="185" t="s">
         <v>170</v>
       </c>
       <c r="G44" s="180" t="s">
@@ -6348,13 +6368,13 @@
       <c r="I44" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="J44" s="184" t="s">
+      <c r="J44" s="185" t="s">
         <v>237</v>
       </c>
-      <c r="K44" s="184" t="s">
+      <c r="K44" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="L44" s="183" t="s">
+      <c r="L44" s="188" t="s">
         <v>224</v>
       </c>
       <c r="M44" s="180" t="s">
@@ -6363,14 +6383,14 @@
       <c r="N44" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="O44" s="187" t="s">
+      <c r="O44" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="P44" s="188"/>
-      <c r="Q44" s="187" t="s">
+      <c r="P44" s="184"/>
+      <c r="Q44" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="R44" s="188"/>
+      <c r="R44" s="184"/>
       <c r="S44" s="32" t="s">
         <v>69</v>
       </c>
@@ -6379,20 +6399,20 @@
       </c>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="182"/>
-      <c r="B45" s="182"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="185"/>
-      <c r="F45" s="185"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="182"/>
-      <c r="I45" s="182"/>
-      <c r="J45" s="185"/>
-      <c r="K45" s="185"/>
-      <c r="L45" s="181"/>
-      <c r="M45" s="182"/>
-      <c r="N45" s="181"/>
+      <c r="A45" s="181"/>
+      <c r="B45" s="181"/>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="186"/>
+      <c r="F45" s="186"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="186"/>
+      <c r="K45" s="186"/>
+      <c r="L45" s="187"/>
+      <c r="M45" s="181"/>
+      <c r="N45" s="187"/>
       <c r="O45" s="27" t="s">
         <v>74</v>
       </c>
@@ -6408,7 +6428,7 @@
       <c r="S45" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T45" s="182"/>
+      <c r="T45" s="181"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="7">
@@ -7030,11 +7050,24 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="M44:M45"/>
-    <mergeCell ref="N44:N45"/>
-    <mergeCell ref="O44:P44"/>
-    <mergeCell ref="Q44:R44"/>
-    <mergeCell ref="T44:T45"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
     <mergeCell ref="L44:L45"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="B44:B45"/>
@@ -7047,24 +7080,11 @@
     <mergeCell ref="I44:I45"/>
     <mergeCell ref="J44:J45"/>
     <mergeCell ref="K44:K45"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="M44:M45"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="T44:T45"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -7252,10 +7272,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="137"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -7265,10 +7285,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="189" t="s">
+      <c r="C14" s="193" t="s">
         <v>240</v>
       </c>
-      <c r="D14" s="137"/>
+      <c r="D14" s="158"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -7294,28 +7314,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="173" t="s">
+      <c r="A17" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="167" t="s">
+      <c r="B18" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="168"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="169"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -7327,12 +7347,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="164"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -7344,12 +7364,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -7361,12 +7381,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -7382,29 +7402,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="170" t="s">
+      <c r="A23" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="171"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="172"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="153"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="148" t="s">
+      <c r="B24" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -7419,14 +7439,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -7440,14 +7460,14 @@
       <c r="A26" s="107">
         <v>2</v>
       </c>
-      <c r="B26" s="150" t="s">
+      <c r="B26" s="138" t="s">
         <v>239</v>
       </c>
-      <c r="C26" s="150"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -7459,12 +7479,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -7493,29 +7513,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="172"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="153"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="148" t="s">
+      <c r="B30" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
+      <c r="C30" s="171"/>
+      <c r="D30" s="171"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -7528,12 +7548,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="172"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -7546,12 +7566,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="155"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="173"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -7563,12 +7583,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="157"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="174"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -7621,31 +7641,31 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="184" t="s">
+      <c r="A37" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="184" t="s">
+      <c r="B37" s="185" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="184" t="s">
+      <c r="D37" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="184" t="s">
+      <c r="E37" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="184" t="s">
+      <c r="F37" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="184" t="s">
+      <c r="G37" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="184" t="s">
+      <c r="H37" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="184" t="s">
+      <c r="I37" s="185" t="s">
         <v>229</v>
       </c>
       <c r="J37" s="180" t="s">
@@ -7662,23 +7682,23 @@
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="184" t="s">
+      <c r="P37" s="185" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="193"/>
-      <c r="B38" s="193"/>
+      <c r="A38" s="189"/>
+      <c r="B38" s="189"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="193"/>
-      <c r="E38" s="185"/>
-      <c r="F38" s="185"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="181"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="186"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="187"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -7694,7 +7714,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="193"/>
+      <c r="P38" s="189"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
@@ -8192,23 +8212,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
@@ -8221,6 +8224,23 @@
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
@@ -8911,10 +8931,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="137"/>
+      <c r="D17" s="158"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -8924,20 +8944,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="137" t="s">
+      <c r="C18" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="137"/>
+      <c r="D18" s="158"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="157" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="137"/>
+      <c r="D19" s="158"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="112" t="s">
@@ -9016,28 +9036,28 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="173" t="s">
+      <c r="A24" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="173"/>
-      <c r="C24" s="173"/>
-      <c r="D24" s="173"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="173"/>
-      <c r="G24" s="173"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="167" t="s">
+      <c r="B25" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="168"/>
-      <c r="D25" s="168"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="169"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136"/>
       <c r="H25" s="95"/>
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
@@ -9054,12 +9074,12 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="106"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
+      <c r="B26" s="164"/>
+      <c r="C26" s="164"/>
+      <c r="D26" s="164"/>
+      <c r="E26" s="164"/>
+      <c r="F26" s="164"/>
+      <c r="G26" s="164"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="J26" s="102"/>
@@ -9076,12 +9096,12 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="107"/>
-      <c r="B27" s="154"/>
-      <c r="C27" s="154"/>
-      <c r="D27" s="154"/>
-      <c r="E27" s="154"/>
-      <c r="F27" s="154"/>
-      <c r="G27" s="154"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="165"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="165"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -9098,12 +9118,12 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="108"/>
-      <c r="B28" s="156"/>
-      <c r="C28" s="156"/>
-      <c r="D28" s="156"/>
-      <c r="E28" s="156"/>
-      <c r="F28" s="156"/>
-      <c r="G28" s="156"/>
+      <c r="B28" s="166"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="166"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -9122,28 +9142,28 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="170" t="s">
+      <c r="A30" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="171"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="172"/>
+      <c r="B30" s="152"/>
+      <c r="C30" s="152"/>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
+      <c r="F30" s="152"/>
+      <c r="G30" s="153"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="148" t="s">
+      <c r="B31" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
+      <c r="C31" s="171"/>
+      <c r="D31" s="171"/>
+      <c r="E31" s="171"/>
+      <c r="F31" s="171"/>
+      <c r="G31" s="171"/>
       <c r="H31" s="95"/>
       <c r="I31" s="95"/>
       <c r="J31" s="95"/>
@@ -9162,14 +9182,14 @@
       <c r="A32" s="106">
         <v>1</v>
       </c>
-      <c r="B32" s="149" t="s">
+      <c r="B32" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="149"/>
-      <c r="E32" s="149"/>
-      <c r="F32" s="149"/>
-      <c r="G32" s="149"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -9186,12 +9206,12 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="107"/>
-      <c r="B33" s="150"/>
-      <c r="C33" s="150"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="150"/>
-      <c r="F33" s="150"/>
-      <c r="G33" s="150"/>
+      <c r="B33" s="138"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -9208,12 +9228,12 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="108"/>
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="151"/>
+      <c r="B34" s="139"/>
+      <c r="C34" s="139"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -9250,28 +9270,28 @@
       <c r="S35"/>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="170" t="s">
+      <c r="A36" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="171"/>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="172"/>
+      <c r="B36" s="152"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
+      <c r="F36" s="152"/>
+      <c r="G36" s="153"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="148" t="s">
+      <c r="B37" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="148"/>
-      <c r="D37" s="148"/>
-      <c r="E37" s="148"/>
-      <c r="F37" s="148"/>
-      <c r="G37" s="148"/>
+      <c r="C37" s="171"/>
+      <c r="D37" s="171"/>
+      <c r="E37" s="171"/>
+      <c r="F37" s="171"/>
+      <c r="G37" s="171"/>
       <c r="H37" s="95"/>
       <c r="I37" s="95"/>
       <c r="J37" s="95"/>
@@ -9288,12 +9308,12 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="106"/>
-      <c r="B38" s="152"/>
-      <c r="C38" s="152"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="153"/>
+      <c r="B38" s="164"/>
+      <c r="C38" s="164"/>
+      <c r="D38" s="164"/>
+      <c r="E38" s="164"/>
+      <c r="F38" s="164"/>
+      <c r="G38" s="172"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -9310,12 +9330,12 @@
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="107"/>
-      <c r="B39" s="154"/>
-      <c r="C39" s="154"/>
-      <c r="D39" s="154"/>
-      <c r="E39" s="154"/>
-      <c r="F39" s="154"/>
-      <c r="G39" s="155"/>
+      <c r="B39" s="165"/>
+      <c r="C39" s="165"/>
+      <c r="D39" s="165"/>
+      <c r="E39" s="165"/>
+      <c r="F39" s="165"/>
+      <c r="G39" s="173"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -9332,12 +9352,12 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="108"/>
-      <c r="B40" s="156"/>
-      <c r="C40" s="156"/>
-      <c r="D40" s="156"/>
-      <c r="E40" s="156"/>
-      <c r="F40" s="156"/>
-      <c r="G40" s="157"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="166"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="174"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -9410,16 +9430,16 @@
       <c r="B44" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="186" t="s">
+      <c r="C44" s="182" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="184" t="s">
+      <c r="E44" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F44" s="184" t="s">
+      <c r="F44" s="185" t="s">
         <v>170</v>
       </c>
       <c r="G44" s="180" t="s">
@@ -9431,13 +9451,13 @@
       <c r="I44" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="J44" s="184" t="s">
+      <c r="J44" s="185" t="s">
         <v>237</v>
       </c>
-      <c r="K44" s="184" t="s">
+      <c r="K44" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="L44" s="183" t="s">
+      <c r="L44" s="188" t="s">
         <v>224</v>
       </c>
       <c r="M44" s="180" t="s">
@@ -9446,14 +9466,14 @@
       <c r="N44" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="O44" s="187" t="s">
+      <c r="O44" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="P44" s="188"/>
-      <c r="Q44" s="187" t="s">
+      <c r="P44" s="184"/>
+      <c r="Q44" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="R44" s="188"/>
+      <c r="R44" s="184"/>
       <c r="S44" s="32" t="s">
         <v>69</v>
       </c>
@@ -9462,20 +9482,20 @@
       </c>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="182"/>
-      <c r="B45" s="182"/>
-      <c r="C45" s="182"/>
-      <c r="D45" s="182"/>
-      <c r="E45" s="185"/>
-      <c r="F45" s="185"/>
-      <c r="G45" s="182"/>
-      <c r="H45" s="182"/>
-      <c r="I45" s="182"/>
-      <c r="J45" s="185"/>
-      <c r="K45" s="185"/>
-      <c r="L45" s="181"/>
-      <c r="M45" s="182"/>
-      <c r="N45" s="181"/>
+      <c r="A45" s="181"/>
+      <c r="B45" s="181"/>
+      <c r="C45" s="181"/>
+      <c r="D45" s="181"/>
+      <c r="E45" s="186"/>
+      <c r="F45" s="186"/>
+      <c r="G45" s="181"/>
+      <c r="H45" s="181"/>
+      <c r="I45" s="181"/>
+      <c r="J45" s="186"/>
+      <c r="K45" s="186"/>
+      <c r="L45" s="187"/>
+      <c r="M45" s="181"/>
+      <c r="N45" s="187"/>
       <c r="O45" s="27" t="s">
         <v>74</v>
       </c>
@@ -9491,7 +9511,7 @@
       <c r="S45" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T45" s="182"/>
+      <c r="T45" s="181"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="7">
@@ -10115,6 +10135,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="N44:N45"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="L44:L45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A24:G24"/>
@@ -10131,25 +10170,6 @@
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
-    <mergeCell ref="N44:N45"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="L44:L45"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="B37:G37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -10204,7 +10224,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10235,7 +10255,7 @@
     <col min="29" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19">
+    <row r="1" spans="1:14" ht="19">
       <c r="A1" s="18" t="s">
         <v>22</v>
       </c>
@@ -10243,17 +10263,17 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="B3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -10261,7 +10281,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="5"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -10272,7 +10292,7 @@
       </c>
       <c r="D6" s="118"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
         <v>80</v>
       </c>
@@ -10283,7 +10303,7 @@
       <c r="D7" s="33"/>
       <c r="N7"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
@@ -10293,7 +10313,7 @@
       </c>
       <c r="D8" s="34"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="4" t="s">
         <v>151</v>
       </c>
@@ -10303,7 +10323,7 @@
       </c>
       <c r="D9" s="85"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="4" t="s">
         <v>231</v>
       </c>
@@ -10314,7 +10334,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -10322,7 +10342,7 @@
       <c r="C11" s="46"/>
       <c r="D11" s="33"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:14">
       <c r="A12" s="4" t="s">
         <v>97</v>
       </c>
@@ -10332,7 +10352,7 @@
       </c>
       <c r="D12" s="33"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14">
       <c r="A13" s="4" t="s">
         <v>257</v>
       </c>
@@ -10345,109 +10365,105 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="111" t="s">
+    <row r="14" spans="1:14">
+      <c r="A14" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="137" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="137"/>
-      <c r="E14" s="1" t="s">
+      <c r="D15" s="158"/>
+      <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="27" customHeight="1">
-      <c r="A15" s="111" t="s">
+    <row r="16" spans="1:14" ht="27" customHeight="1">
+      <c r="A16" s="111" t="s">
         <v>170</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="189" t="s">
+      <c r="B16" s="111"/>
+      <c r="C16" s="193" t="s">
         <v>240</v>
       </c>
-      <c r="D15" s="137"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="112" t="s">
+      <c r="D16" s="158"/>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="113"/>
-      <c r="C16" s="90" t="s">
+      <c r="B17" s="113"/>
+      <c r="C17" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>173</v>
       </c>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-    </row>
-    <row r="17" spans="1:17">
-      <c r="A17" s="6"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="173" t="s">
+      <c r="A18" s="6"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B18" s="173"/>
-      <c r="C18" s="173"/>
-      <c r="D18" s="173"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="173"/>
-      <c r="G18" s="173"/>
-    </row>
-    <row r="19" spans="1:17">
-      <c r="A19" s="105" t="s">
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="167" t="s">
+      <c r="B20" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="168"/>
-      <c r="D19" s="168"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="169"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="95"/>
-      <c r="P19" s="101"/>
-      <c r="Q19" s="101"/>
-    </row>
-    <row r="20" spans="1:17">
-      <c r="A20" s="106"/>
-      <c r="B20" s="152"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="102"/>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="95"/>
+      <c r="I20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="95"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="101"/>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="107"/>
-      <c r="B21" s="154"/>
-      <c r="C21" s="154"/>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="154"/>
+      <c r="A21" s="106"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="164"/>
+      <c r="G21" s="164"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -10458,16 +10474,15 @@
       <c r="Q21"/>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="108"/>
-      <c r="B22" s="156"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="156"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="156"/>
-      <c r="G22" s="156"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
-      <c r="J22" s="95"/>
       <c r="K22" s="102"/>
       <c r="L22" s="102"/>
       <c r="M22" s="102"/>
@@ -10476,76 +10491,73 @@
       <c r="Q22"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="C23"/>
-      <c r="J23" s="102"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="166"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
+      <c r="H23" s="102"/>
+      <c r="I23" s="102"/>
+      <c r="J23" s="95"/>
+      <c r="K23" s="102"/>
+      <c r="L23" s="102"/>
+      <c r="M23" s="102"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="170" t="s">
+      <c r="C24"/>
+      <c r="J24" s="102"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B24" s="171"/>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="172"/>
-      <c r="J24" s="102"/>
-    </row>
-    <row r="25" spans="1:17">
-      <c r="A25" s="105" t="s">
+      <c r="B25" s="152"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="153"/>
+      <c r="J25" s="102"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="148" t="s">
+      <c r="B26" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="148"/>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="102"/>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="95"/>
-      <c r="N25" s="95"/>
-      <c r="P25" s="101"/>
-      <c r="Q25" s="101"/>
-    </row>
-    <row r="26" spans="1:17">
-      <c r="A26" s="106">
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="102"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="P26" s="101"/>
+      <c r="Q26" s="101"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B26" s="149" t="s">
+      <c r="B27" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="149"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="149"/>
-      <c r="H26" s="102"/>
-      <c r="I26" s="102"/>
-      <c r="K26" s="102"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="102"/>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-    </row>
-    <row r="27" spans="1:17">
-      <c r="A27" s="107">
-        <v>2</v>
-      </c>
-      <c r="B27" s="150" t="s">
-        <v>239</v>
-      </c>
-      <c r="C27" s="150"/>
-      <c r="D27" s="150"/>
-      <c r="E27" s="150"/>
-      <c r="F27" s="150"/>
-      <c r="G27" s="150"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -10556,16 +10568,19 @@
       <c r="Q27"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="108"/>
-      <c r="B28" s="151"/>
-      <c r="C28" s="151"/>
-      <c r="D28" s="151"/>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
+      <c r="A28" s="107">
+        <v>2</v>
+      </c>
+      <c r="B28" s="138" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
-      <c r="J28" s="95"/>
       <c r="K28" s="102"/>
       <c r="L28" s="102"/>
       <c r="M28" s="102"/>
@@ -10574,84 +10589,85 @@
       <c r="Q28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29"/>
-      <c r="B29"/>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29"/>
-      <c r="H29"/>
-      <c r="I29"/>
-      <c r="J29" s="102"/>
-      <c r="K29"/>
-      <c r="L29"/>
-      <c r="M29"/>
-      <c r="N29"/>
+      <c r="A29" s="108"/>
+      <c r="B29" s="139"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="95"/>
+      <c r="K29" s="102"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
       <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="170" t="s">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30" s="102"/>
+      <c r="K30"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="171"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="172"/>
-      <c r="J30" s="102"/>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="105" t="s">
+      <c r="B31" s="152"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="153"/>
+      <c r="J31" s="102"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="148" t="s">
+      <c r="B32" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C31" s="148"/>
-      <c r="D31" s="148"/>
-      <c r="E31" s="148"/>
-      <c r="F31" s="148"/>
-      <c r="G31" s="148"/>
-      <c r="H31" s="95"/>
-      <c r="I31" s="95"/>
-      <c r="J31" s="102"/>
-      <c r="K31" s="95"/>
-      <c r="L31" s="95"/>
-      <c r="M31" s="95"/>
-      <c r="N31" s="95"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="101"/>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="106"/>
-      <c r="B32" s="152"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152"/>
-      <c r="G32" s="153"/>
-      <c r="H32" s="102"/>
-      <c r="I32" s="102"/>
-      <c r="J32"/>
-      <c r="K32" s="102"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="102"/>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32"/>
+      <c r="C32" s="171"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
+      <c r="H32" s="95"/>
+      <c r="I32" s="95"/>
+      <c r="J32" s="102"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
+      <c r="M32" s="95"/>
+      <c r="N32" s="95"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="101"/>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="107"/>
-      <c r="B33" s="154"/>
-      <c r="C33" s="154"/>
-      <c r="D33" s="154"/>
-      <c r="E33" s="154"/>
-      <c r="F33" s="154"/>
-      <c r="G33" s="155"/>
+      <c r="A33" s="106"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="172"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
+      <c r="J33"/>
       <c r="K33" s="102"/>
       <c r="L33" s="102"/>
       <c r="M33" s="102"/>
@@ -10660,16 +10676,15 @@
       <c r="Q33"/>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="108"/>
-      <c r="B34" s="156"/>
-      <c r="C34" s="156"/>
-      <c r="D34" s="156"/>
-      <c r="E34" s="156"/>
-      <c r="F34" s="156"/>
-      <c r="G34" s="157"/>
+      <c r="A34" s="107"/>
+      <c r="B34" s="165"/>
+      <c r="C34" s="165"/>
+      <c r="D34" s="165"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="173"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
-      <c r="J34" s="95"/>
       <c r="K34" s="102"/>
       <c r="L34" s="102"/>
       <c r="M34" s="102"/>
@@ -10678,194 +10693,186 @@
       <c r="Q34"/>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-      <c r="I35"/>
-      <c r="J35" s="102"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
+      <c r="A35" s="108"/>
+      <c r="B35" s="166"/>
+      <c r="C35" s="166"/>
+      <c r="D35" s="166"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="174"/>
+      <c r="H35" s="102"/>
+      <c r="I35" s="102"/>
+      <c r="J35" s="95"/>
+      <c r="K35" s="102"/>
+      <c r="L35" s="102"/>
+      <c r="M35" s="102"/>
       <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="6"/>
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
       <c r="J36" s="102"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" s="47" t="s">
+      <c r="A37" s="6"/>
+      <c r="J37" s="102"/>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="116"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="48"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="49"/>
-    </row>
-    <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="184" t="s">
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="116"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="49"/>
+    </row>
+    <row r="39" spans="1:17" ht="15">
+      <c r="A39" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B38" s="184" t="s">
+      <c r="B39" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D38" s="184" t="s">
+      <c r="D39" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E38" s="184" t="s">
+      <c r="E39" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F38" s="184" t="s">
+      <c r="F39" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G38" s="184" t="s">
+      <c r="G39" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="H38" s="184" t="s">
+      <c r="H39" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="184" t="s">
+      <c r="I39" s="185" t="s">
         <v>229</v>
       </c>
-      <c r="J38" s="180" t="s">
+      <c r="J39" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="K38" s="190" t="s">
+      <c r="K39" s="190" t="s">
         <v>119</v>
       </c>
-      <c r="L38" s="191"/>
-      <c r="M38" s="192" t="s">
+      <c r="L39" s="191"/>
+      <c r="M39" s="192" t="s">
         <v>120</v>
       </c>
-      <c r="N38" s="191"/>
-      <c r="O38" s="50" t="s">
+      <c r="N39" s="191"/>
+      <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P38" s="184" t="s">
+      <c r="P39" s="185" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="193"/>
-      <c r="B39" s="193"/>
-      <c r="C39" s="52" t="s">
+    <row r="40" spans="1:17" ht="15">
+      <c r="A40" s="189"/>
+      <c r="B40" s="189"/>
+      <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="193"/>
-      <c r="E39" s="185"/>
-      <c r="F39" s="185"/>
-      <c r="G39" s="193"/>
-      <c r="H39" s="193"/>
-      <c r="I39" s="193"/>
-      <c r="J39" s="181"/>
-      <c r="K39" s="53" t="s">
+      <c r="D40" s="189"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="187"/>
+      <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="L39" s="53" t="s">
+      <c r="L40" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="M39" s="53" t="s">
+      <c r="M40" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="N39" s="53" t="s">
+      <c r="N40" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="O39" s="54" t="s">
+      <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P39" s="193"/>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="55">
-        <v>1</v>
-      </c>
-      <c r="B40" s="56" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="57" t="s">
-        <v>128</v>
-      </c>
-      <c r="D40" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="80"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
-      <c r="P40" s="59"/>
+      <c r="P40" s="189"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" s="56" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D41" s="58" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E41" s="58"/>
       <c r="F41" s="58"/>
       <c r="G41" s="80"/>
       <c r="H41" s="58"/>
       <c r="I41" s="58"/>
-      <c r="J41" s="24" t="s">
+      <c r="J41" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="K41" s="56"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="56"/>
-      <c r="O41" s="56"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
       <c r="P41" s="59"/>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="55">
-        <v>3</v>
-      </c>
-      <c r="B42" s="60" t="s">
-        <v>132</v>
-      </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
+        <v>2</v>
+      </c>
+      <c r="B42" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
       <c r="J42" s="24" t="s">
         <v>137</v>
       </c>
@@ -10874,24 +10881,24 @@
       <c r="M42" s="56"/>
       <c r="N42" s="56"/>
       <c r="O42" s="56"/>
-      <c r="P42" s="62"/>
+      <c r="P42" s="59"/>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="55">
-        <v>4</v>
-      </c>
-      <c r="B43" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
+        <v>3</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="45"/>
+      <c r="D43" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="E43" s="61"/>
+      <c r="F43" s="61"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="61"/>
+      <c r="I43" s="61"/>
       <c r="J43" s="24" t="s">
         <v>137</v>
       </c>
@@ -10900,48 +10907,48 @@
       <c r="M43" s="56"/>
       <c r="N43" s="56"/>
       <c r="O43" s="56"/>
-      <c r="P43" s="66"/>
+      <c r="P43" s="62"/>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="55">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" s="63" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C44" s="64"/>
       <c r="D44" s="65" t="s">
-        <v>107</v>
-      </c>
-      <c r="E44" s="65" t="s">
-        <v>166</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="E44" s="65"/>
       <c r="F44" s="65"/>
-      <c r="G44" s="82"/>
+      <c r="G44" s="84"/>
       <c r="H44" s="65"/>
       <c r="I44" s="65"/>
       <c r="J44" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="K44" s="58"/>
-      <c r="L44" s="58"/>
-      <c r="M44" s="58"/>
-      <c r="N44" s="58"/>
-      <c r="O44" s="58"/>
+      <c r="K44" s="56"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="56"/>
+      <c r="O44" s="56"/>
       <c r="P44" s="66"/>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="55">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B45" s="63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C45" s="64"/>
       <c r="D45" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" s="65"/>
+        <v>107</v>
+      </c>
+      <c r="E45" s="65" t="s">
+        <v>166</v>
+      </c>
       <c r="F45" s="65"/>
       <c r="G45" s="82"/>
       <c r="H45" s="65"/>
@@ -10949,23 +10956,23 @@
       <c r="J45" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="K45" s="56"/>
-      <c r="L45" s="56"/>
-      <c r="M45" s="56"/>
-      <c r="N45" s="56"/>
-      <c r="O45" s="56"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
       <c r="P45" s="66"/>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B46" s="63" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="C46" s="64"/>
       <c r="D46" s="65" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="E46" s="65"/>
       <c r="F46" s="65"/>
@@ -10983,16 +10990,24 @@
       <c r="P46" s="66"/>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="55"/>
-      <c r="B47" s="63"/>
+      <c r="A47" s="55">
+        <v>7</v>
+      </c>
+      <c r="B47" s="63" t="s">
+        <v>111</v>
+      </c>
       <c r="C47" s="64"/>
-      <c r="D47" s="65"/>
+      <c r="D47" s="65" t="s">
+        <v>258</v>
+      </c>
       <c r="E47" s="65"/>
       <c r="F47" s="65"/>
       <c r="G47" s="82"/>
       <c r="H47" s="65"/>
       <c r="I47" s="65"/>
-      <c r="J47" s="24"/>
+      <c r="J47" s="24" t="s">
+        <v>137</v>
+      </c>
       <c r="K47" s="56"/>
       <c r="L47" s="56"/>
       <c r="M47" s="56"/>
@@ -11011,11 +11026,11 @@
       <c r="H48" s="65"/>
       <c r="I48" s="65"/>
       <c r="J48" s="24"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-      <c r="O48" s="58"/>
+      <c r="K48" s="56"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="56"/>
+      <c r="N48" s="56"/>
+      <c r="O48" s="56"/>
       <c r="P48" s="66"/>
     </row>
     <row r="49" spans="1:16">
@@ -11029,11 +11044,11 @@
       <c r="H49" s="65"/>
       <c r="I49" s="65"/>
       <c r="J49" s="24"/>
-      <c r="K49" s="56"/>
-      <c r="L49" s="56"/>
-      <c r="M49" s="56"/>
-      <c r="N49" s="56"/>
-      <c r="O49" s="56"/>
+      <c r="K49" s="58"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
       <c r="P49" s="66"/>
     </row>
     <row r="50" spans="1:16">
@@ -11119,11 +11134,11 @@
       <c r="H54" s="65"/>
       <c r="I54" s="65"/>
       <c r="J54" s="24"/>
-      <c r="K54" s="58"/>
-      <c r="L54" s="58"/>
-      <c r="M54" s="58"/>
-      <c r="N54" s="58"/>
-      <c r="O54" s="58"/>
+      <c r="K54" s="56"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="56"/>
+      <c r="N54" s="56"/>
+      <c r="O54" s="56"/>
       <c r="P54" s="66"/>
     </row>
     <row r="55" spans="1:16">
@@ -11137,11 +11152,11 @@
       <c r="H55" s="65"/>
       <c r="I55" s="65"/>
       <c r="J55" s="24"/>
-      <c r="K55" s="56"/>
-      <c r="L55" s="56"/>
-      <c r="M55" s="56"/>
-      <c r="N55" s="56"/>
-      <c r="O55" s="56"/>
+      <c r="K55" s="58"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
       <c r="P55" s="66"/>
     </row>
     <row r="56" spans="1:16">
@@ -11209,11 +11224,11 @@
       <c r="H59" s="65"/>
       <c r="I59" s="65"/>
       <c r="J59" s="24"/>
-      <c r="K59" s="58"/>
-      <c r="L59" s="58"/>
-      <c r="M59" s="58"/>
-      <c r="N59" s="58"/>
-      <c r="O59" s="58"/>
+      <c r="K59" s="56"/>
+      <c r="L59" s="56"/>
+      <c r="M59" s="56"/>
+      <c r="N59" s="56"/>
+      <c r="O59" s="56"/>
       <c r="P59" s="66"/>
     </row>
     <row r="60" spans="1:16">
@@ -11227,11 +11242,11 @@
       <c r="H60" s="65"/>
       <c r="I60" s="65"/>
       <c r="J60" s="24"/>
-      <c r="K60" s="56"/>
-      <c r="L60" s="56"/>
-      <c r="M60" s="56"/>
-      <c r="N60" s="56"/>
-      <c r="O60" s="56"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
       <c r="P60" s="66"/>
     </row>
     <row r="61" spans="1:16">
@@ -11263,72 +11278,90 @@
       <c r="H62" s="65"/>
       <c r="I62" s="65"/>
       <c r="J62" s="24"/>
-      <c r="K62" s="58"/>
-      <c r="L62" s="58"/>
-      <c r="M62" s="58"/>
-      <c r="N62" s="58"/>
-      <c r="O62" s="58"/>
+      <c r="K62" s="56"/>
+      <c r="L62" s="56"/>
+      <c r="M62" s="56"/>
+      <c r="N62" s="56"/>
+      <c r="O62" s="56"/>
       <c r="P62" s="66"/>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="67"/>
-      <c r="B63" s="68"/>
-      <c r="C63" s="69"/>
-      <c r="D63" s="70"/>
-      <c r="E63" s="70"/>
-      <c r="F63" s="70"/>
-      <c r="G63" s="83"/>
-      <c r="H63" s="70"/>
-      <c r="I63" s="70"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="71"/>
-      <c r="L63" s="71"/>
-      <c r="M63" s="71"/>
-      <c r="N63" s="71"/>
-      <c r="O63" s="71"/>
-      <c r="P63" s="72"/>
+      <c r="A63" s="55"/>
+      <c r="B63" s="63"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="65"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="82"/>
+      <c r="H63" s="65"/>
+      <c r="I63" s="65"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="66"/>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" s="67"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="69"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="70"/>
+      <c r="F64" s="70"/>
+      <c r="G64" s="83"/>
+      <c r="H64" s="70"/>
+      <c r="I64" s="70"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="71"/>
+      <c r="L64" s="71"/>
+      <c r="M64" s="71"/>
+      <c r="N64" s="71"/>
+      <c r="O64" s="71"/>
+      <c r="P64" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="I38:I39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="P38:P39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
-    <mergeCell ref="J38:J39"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>Validate実装パターン</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16" xr:uid="{701F546D-1FF6-BD4A-B0C0-0C5ED6D3FBB2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17" xr:uid="{701F546D-1FF6-BD4A-B0C0-0C5ED6D3FBB2}">
       <formula1>isImport</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J40:J63" xr:uid="{92A7294B-4CDA-CF4D-AAF2-996905462F96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J41:J64" xr:uid="{92A7294B-4CDA-CF4D-AAF2-996905462F96}">
       <formula1>isNullable</formula1>
     </dataValidation>
   </dataValidations>
@@ -11345,7 +11378,7 @@
           <x14:formula1>
             <xm:f>config!$B$5:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G40:G63</xm:sqref>
+          <xm:sqref>G41:G64</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000002000000}">
           <x14:formula1>
@@ -11523,10 +11556,10 @@
         <v>167</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="137"/>
+      <c r="D15" s="158"/>
       <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
@@ -11536,10 +11569,10 @@
         <v>170</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="137" t="s">
+      <c r="C16" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="137"/>
+      <c r="D16" s="158"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="112" t="s">
@@ -11565,28 +11598,28 @@
       <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="173" t="s">
+      <c r="A19" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="173"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="167" t="s">
+      <c r="B20" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="168"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="169"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="95"/>
       <c r="I20" s="95"/>
       <c r="K20" s="95"/>
@@ -11598,12 +11631,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="106"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="164"/>
+      <c r="G21" s="164"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -11615,12 +11648,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="107"/>
-      <c r="B22" s="154"/>
-      <c r="C22" s="154"/>
-      <c r="D22" s="154"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="K22" s="102"/>
@@ -11632,12 +11665,12 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="108"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
+      <c r="B23" s="166"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
       <c r="H23" s="102"/>
       <c r="I23" s="102"/>
       <c r="J23" s="95"/>
@@ -11653,29 +11686,29 @@
       <c r="J24" s="102"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="170" t="s">
+      <c r="A25" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="171"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="172"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="153"/>
       <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="148" t="s">
+      <c r="B26" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="102"/>
@@ -11690,14 +11723,14 @@
       <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B27" s="149" t="s">
+      <c r="B27" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
-      <c r="G27" s="149"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -11709,12 +11742,12 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="107"/>
-      <c r="B28" s="150"/>
-      <c r="C28" s="150"/>
-      <c r="D28" s="150"/>
-      <c r="E28" s="150"/>
-      <c r="F28" s="150"/>
-      <c r="G28" s="150"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="K28" s="102"/>
@@ -11726,12 +11759,12 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="108"/>
-      <c r="B29" s="151"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
+      <c r="B29" s="139"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="95"/>
@@ -11760,29 +11793,29 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="170" t="s">
+      <c r="A31" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="171"/>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="172"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="153"/>
       <c r="J31" s="102"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="148" t="s">
+      <c r="B32" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="148"/>
-      <c r="D32" s="148"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
+      <c r="C32" s="171"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
       <c r="H32" s="95"/>
       <c r="I32" s="95"/>
       <c r="J32" s="102"/>
@@ -11795,12 +11828,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="106"/>
-      <c r="B33" s="152"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
-      <c r="F33" s="152"/>
-      <c r="G33" s="153"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="172"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33"/>
@@ -11813,12 +11846,12 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="107"/>
-      <c r="B34" s="154"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="154"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="155"/>
+      <c r="B34" s="165"/>
+      <c r="C34" s="165"/>
+      <c r="D34" s="165"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="173"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="K34" s="102"/>
@@ -11830,12 +11863,12 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="108"/>
-      <c r="B35" s="156"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="156"/>
-      <c r="G35" s="157"/>
+      <c r="B35" s="166"/>
+      <c r="C35" s="166"/>
+      <c r="D35" s="166"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="174"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="95"/>
@@ -11888,25 +11921,25 @@
       <c r="P38" s="49"/>
     </row>
     <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="184" t="s">
+      <c r="A39" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="184" t="s">
+      <c r="B39" s="185" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="184" t="s">
+      <c r="D39" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="184" t="s">
+      <c r="E39" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="184" t="s">
+      <c r="F39" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G39" s="184" t="s">
+      <c r="G39" s="185" t="s">
         <v>136</v>
       </c>
       <c r="H39" s="194" t="s">
@@ -11929,23 +11962,23 @@
       <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P39" s="184" t="s">
+      <c r="P39" s="185" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15">
-      <c r="A40" s="193"/>
-      <c r="B40" s="193"/>
+      <c r="A40" s="189"/>
+      <c r="B40" s="189"/>
       <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="193"/>
-      <c r="E40" s="185"/>
-      <c r="F40" s="185"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="181"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="187"/>
       <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
@@ -11961,7 +11994,7 @@
       <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P40" s="193"/>
+      <c r="P40" s="189"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
@@ -12417,6 +12450,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="P39:P40"/>
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="B32:G32"/>
@@ -12433,19 +12479,6 @@
     <mergeCell ref="J39:J40"/>
     <mergeCell ref="K39:L39"/>
     <mergeCell ref="M39:N39"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
@@ -12662,10 +12695,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="137"/>
+      <c r="D17" s="158"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -12675,20 +12708,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="137" t="s">
+      <c r="C18" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="137"/>
+      <c r="D18" s="158"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="157" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="137"/>
+      <c r="D19" s="158"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="112" t="s">
@@ -12772,15 +12805,15 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="154" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="176"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="156"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="91" t="s">
@@ -12828,28 +12861,28 @@
       <c r="C28"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="173" t="s">
+      <c r="A29" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="168"/>
-      <c r="D30" s="168"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="169"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="136"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="95"/>
@@ -12867,12 +12900,12 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="106"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="164"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31" s="102"/>
@@ -12890,12 +12923,12 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="107"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="165"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -12913,12 +12946,12 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="108"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="166"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -12938,28 +12971,28 @@
       <c r="C34"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="170" t="s">
+      <c r="A35" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B35" s="171"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="172"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="153"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="148" t="s">
+      <c r="B36" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="148"/>
-      <c r="D36" s="148"/>
-      <c r="E36" s="148"/>
-      <c r="F36" s="148"/>
-      <c r="G36" s="148"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
+      <c r="E36" s="171"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="95"/>
       <c r="I36" s="95"/>
       <c r="J36" s="95"/>
@@ -12979,14 +13012,14 @@
       <c r="A37" s="106">
         <v>1</v>
       </c>
-      <c r="B37" s="149" t="s">
+      <c r="B37" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="149"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="137"/>
       <c r="H37" s="102"/>
       <c r="I37" s="102"/>
       <c r="J37" s="102"/>
@@ -13004,12 +13037,12 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="107"/>
-      <c r="B38" s="150"/>
-      <c r="C38" s="150"/>
-      <c r="D38" s="150"/>
-      <c r="E38" s="150"/>
-      <c r="F38" s="150"/>
-      <c r="G38" s="150"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -13027,12 +13060,12 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="108"/>
-      <c r="B39" s="151"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
+      <c r="B39" s="139"/>
+      <c r="C39" s="139"/>
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -13071,28 +13104,28 @@
       <c r="T40"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="170" t="s">
+      <c r="A41" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="171"/>
-      <c r="C41" s="171"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="172"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="152"/>
+      <c r="D41" s="152"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="152"/>
+      <c r="G41" s="153"/>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="148" t="s">
+      <c r="B42" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="148"/>
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
+      <c r="C42" s="171"/>
+      <c r="D42" s="171"/>
+      <c r="E42" s="171"/>
+      <c r="F42" s="171"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="95"/>
       <c r="I42" s="95"/>
       <c r="J42" s="95"/>
@@ -13110,12 +13143,12 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="106"/>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
-      <c r="F43" s="152"/>
-      <c r="G43" s="153"/>
+      <c r="B43" s="164"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="172"/>
       <c r="H43" s="102"/>
       <c r="I43" s="102"/>
       <c r="J43" s="102"/>
@@ -13133,12 +13166,12 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="107"/>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="154"/>
-      <c r="E44" s="154"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="155"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="165"/>
+      <c r="E44" s="165"/>
+      <c r="F44" s="165"/>
+      <c r="G44" s="173"/>
       <c r="H44" s="102"/>
       <c r="I44" s="102"/>
       <c r="J44" s="102"/>
@@ -13156,12 +13189,12 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="108"/>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
-      <c r="D45" s="156"/>
-      <c r="E45" s="156"/>
-      <c r="F45" s="156"/>
-      <c r="G45" s="157"/>
+      <c r="B45" s="166"/>
+      <c r="C45" s="166"/>
+      <c r="D45" s="166"/>
+      <c r="E45" s="166"/>
+      <c r="F45" s="166"/>
+      <c r="G45" s="174"/>
       <c r="H45" s="102"/>
       <c r="I45" s="102"/>
       <c r="J45" s="102"/>
@@ -13237,16 +13270,16 @@
       <c r="B49" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="186" t="s">
+      <c r="C49" s="182" t="s">
         <v>1</v>
       </c>
       <c r="D49" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="184" t="s">
+      <c r="E49" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="184" t="s">
+      <c r="F49" s="185" t="s">
         <v>170</v>
       </c>
       <c r="G49" s="180" t="s">
@@ -13258,13 +13291,13 @@
       <c r="I49" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="J49" s="184" t="s">
+      <c r="J49" s="185" t="s">
         <v>237</v>
       </c>
-      <c r="K49" s="184" t="s">
+      <c r="K49" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="L49" s="183" t="s">
+      <c r="L49" s="188" t="s">
         <v>224</v>
       </c>
       <c r="M49" s="180" t="s">
@@ -13276,14 +13309,14 @@
       <c r="O49" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="P49" s="187" t="s">
+      <c r="P49" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="Q49" s="188"/>
-      <c r="R49" s="187" t="s">
+      <c r="Q49" s="184"/>
+      <c r="R49" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="S49" s="188"/>
+      <c r="S49" s="184"/>
       <c r="T49" s="32" t="s">
         <v>69</v>
       </c>
@@ -13292,21 +13325,21 @@
       </c>
     </row>
     <row r="50" spans="1:21">
-      <c r="A50" s="182"/>
-      <c r="B50" s="182"/>
-      <c r="C50" s="182"/>
-      <c r="D50" s="182"/>
-      <c r="E50" s="185"/>
-      <c r="F50" s="185"/>
-      <c r="G50" s="182"/>
-      <c r="H50" s="182"/>
-      <c r="I50" s="182"/>
-      <c r="J50" s="185"/>
-      <c r="K50" s="185"/>
-      <c r="L50" s="181"/>
-      <c r="M50" s="182"/>
-      <c r="N50" s="182"/>
-      <c r="O50" s="181"/>
+      <c r="A50" s="181"/>
+      <c r="B50" s="181"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="186"/>
+      <c r="F50" s="186"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="186"/>
+      <c r="K50" s="186"/>
+      <c r="L50" s="187"/>
+      <c r="M50" s="181"/>
+      <c r="N50" s="181"/>
+      <c r="O50" s="187"/>
       <c r="P50" s="27" t="s">
         <v>74</v>
       </c>
@@ -13322,7 +13355,7 @@
       <c r="T50" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U50" s="182"/>
+      <c r="U50" s="181"/>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="7">
@@ -13966,6 +13999,30 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="U49:U50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
@@ -13979,30 +14036,6 @@
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="U49:U50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="R49:S49"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -14190,10 +14223,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="137"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -14203,10 +14236,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="137" t="s">
+      <c r="C14" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="137"/>
+      <c r="D14" s="158"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -14232,28 +14265,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="173" t="s">
+      <c r="A17" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="167" t="s">
+      <c r="B18" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="168"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="169"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -14265,12 +14298,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="164"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -14282,12 +14315,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -14299,12 +14332,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -14320,29 +14353,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="170" t="s">
+      <c r="A23" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="171"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="172"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="153"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="148" t="s">
+      <c r="B24" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -14357,14 +14390,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -14376,12 +14409,12 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="107"/>
-      <c r="B26" s="150"/>
-      <c r="C26" s="150"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -14393,12 +14426,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -14427,29 +14460,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="172"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="153"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="148" t="s">
+      <c r="B30" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
+      <c r="C30" s="171"/>
+      <c r="D30" s="171"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -14462,12 +14495,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="172"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -14480,12 +14513,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="155"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="173"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -14497,12 +14530,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="157"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="174"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -14555,31 +14588,31 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="184" t="s">
+      <c r="A37" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="184" t="s">
+      <c r="B37" s="185" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="184" t="s">
+      <c r="D37" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="184" t="s">
+      <c r="E37" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="184" t="s">
+      <c r="F37" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="184" t="s">
+      <c r="G37" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="184" t="s">
+      <c r="H37" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="184" t="s">
+      <c r="I37" s="185" t="s">
         <v>229</v>
       </c>
       <c r="J37" s="180" t="s">
@@ -14596,23 +14629,23 @@
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="184" t="s">
+      <c r="P37" s="185" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="193"/>
-      <c r="B38" s="193"/>
+      <c r="A38" s="189"/>
+      <c r="B38" s="189"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="193"/>
-      <c r="E38" s="185"/>
-      <c r="F38" s="185"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="181"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="186"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="187"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -14628,7 +14661,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="193"/>
+      <c r="P38" s="189"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
@@ -15126,6 +15159,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
@@ -15138,23 +15188,6 @@
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
@@ -15359,10 +15392,10 @@
         <v>167</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="137"/>
+      <c r="D15" s="158"/>
       <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
@@ -15372,10 +15405,10 @@
         <v>170</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="137" t="s">
+      <c r="C16" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="137"/>
+      <c r="D16" s="158"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="112" t="s">
@@ -15401,28 +15434,28 @@
       <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="173" t="s">
+      <c r="A19" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="173"/>
-      <c r="C19" s="173"/>
-      <c r="D19" s="173"/>
-      <c r="E19" s="173"/>
-      <c r="F19" s="173"/>
-      <c r="G19" s="173"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="167" t="s">
+      <c r="B20" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="168"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="169"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
       <c r="H20" s="95"/>
       <c r="I20" s="95"/>
       <c r="K20" s="95"/>
@@ -15434,12 +15467,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="106"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
-      <c r="F21" s="152"/>
-      <c r="G21" s="152"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="164"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="164"/>
+      <c r="G21" s="164"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -15451,12 +15484,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="107"/>
-      <c r="B22" s="154"/>
-      <c r="C22" s="154"/>
-      <c r="D22" s="154"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
-      <c r="G22" s="154"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
+      <c r="G22" s="165"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="K22" s="102"/>
@@ -15468,12 +15501,12 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="108"/>
-      <c r="B23" s="156"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
+      <c r="B23" s="166"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="166"/>
+      <c r="F23" s="166"/>
+      <c r="G23" s="166"/>
       <c r="H23" s="102"/>
       <c r="I23" s="102"/>
       <c r="J23" s="95"/>
@@ -15489,29 +15522,29 @@
       <c r="J24" s="102"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="170" t="s">
+      <c r="A25" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="171"/>
-      <c r="C25" s="171"/>
-      <c r="D25" s="171"/>
-      <c r="E25" s="171"/>
-      <c r="F25" s="171"/>
-      <c r="G25" s="172"/>
+      <c r="B25" s="152"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
+      <c r="F25" s="152"/>
+      <c r="G25" s="153"/>
       <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="148" t="s">
+      <c r="B26" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="148"/>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
+      <c r="G26" s="171"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="102"/>
@@ -15526,14 +15559,14 @@
       <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B27" s="149" t="s">
+      <c r="B27" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
-      <c r="G27" s="149"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -15545,12 +15578,12 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="107"/>
-      <c r="B28" s="150"/>
-      <c r="C28" s="150"/>
-      <c r="D28" s="150"/>
-      <c r="E28" s="150"/>
-      <c r="F28" s="150"/>
-      <c r="G28" s="150"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="K28" s="102"/>
@@ -15562,12 +15595,12 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="108"/>
-      <c r="B29" s="151"/>
-      <c r="C29" s="151"/>
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
+      <c r="B29" s="139"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
+      <c r="G29" s="139"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="95"/>
@@ -15596,29 +15629,29 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="170" t="s">
+      <c r="A31" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="171"/>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="172"/>
+      <c r="B31" s="152"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
+      <c r="F31" s="152"/>
+      <c r="G31" s="153"/>
       <c r="J31" s="102"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="148" t="s">
+      <c r="B32" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="148"/>
-      <c r="D32" s="148"/>
-      <c r="E32" s="148"/>
-      <c r="F32" s="148"/>
-      <c r="G32" s="148"/>
+      <c r="C32" s="171"/>
+      <c r="D32" s="171"/>
+      <c r="E32" s="171"/>
+      <c r="F32" s="171"/>
+      <c r="G32" s="171"/>
       <c r="H32" s="95"/>
       <c r="I32" s="95"/>
       <c r="J32" s="102"/>
@@ -15631,12 +15664,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="106"/>
-      <c r="B33" s="152"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
-      <c r="F33" s="152"/>
-      <c r="G33" s="153"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="164"/>
+      <c r="D33" s="164"/>
+      <c r="E33" s="164"/>
+      <c r="F33" s="164"/>
+      <c r="G33" s="172"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33"/>
@@ -15649,12 +15682,12 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="107"/>
-      <c r="B34" s="154"/>
-      <c r="C34" s="154"/>
-      <c r="D34" s="154"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="155"/>
+      <c r="B34" s="165"/>
+      <c r="C34" s="165"/>
+      <c r="D34" s="165"/>
+      <c r="E34" s="165"/>
+      <c r="F34" s="165"/>
+      <c r="G34" s="173"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="K34" s="102"/>
@@ -15666,12 +15699,12 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="108"/>
-      <c r="B35" s="156"/>
-      <c r="C35" s="156"/>
-      <c r="D35" s="156"/>
-      <c r="E35" s="156"/>
-      <c r="F35" s="156"/>
-      <c r="G35" s="157"/>
+      <c r="B35" s="166"/>
+      <c r="C35" s="166"/>
+      <c r="D35" s="166"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="174"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="95"/>
@@ -15724,25 +15757,25 @@
       <c r="P38" s="49"/>
     </row>
     <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="184" t="s">
+      <c r="A39" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="184" t="s">
+      <c r="B39" s="185" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="184" t="s">
+      <c r="D39" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="184" t="s">
+      <c r="E39" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="184" t="s">
+      <c r="F39" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G39" s="184" t="s">
+      <c r="G39" s="185" t="s">
         <v>136</v>
       </c>
       <c r="H39" s="194" t="s">
@@ -15765,23 +15798,23 @@
       <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P39" s="184" t="s">
+      <c r="P39" s="185" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15">
-      <c r="A40" s="193"/>
-      <c r="B40" s="193"/>
+      <c r="A40" s="189"/>
+      <c r="B40" s="189"/>
       <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="193"/>
-      <c r="E40" s="185"/>
-      <c r="F40" s="185"/>
-      <c r="G40" s="193"/>
-      <c r="H40" s="193"/>
-      <c r="I40" s="193"/>
-      <c r="J40" s="181"/>
+      <c r="D40" s="189"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="186"/>
+      <c r="G40" s="189"/>
+      <c r="H40" s="189"/>
+      <c r="I40" s="189"/>
+      <c r="J40" s="187"/>
       <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
@@ -15797,7 +15830,7 @@
       <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P40" s="193"/>
+      <c r="P40" s="189"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
@@ -16253,6 +16286,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="J39:J40"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
     <mergeCell ref="B29:G29"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
@@ -16265,23 +16315,6 @@
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:G28"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="J39:J40"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">
@@ -16498,10 +16531,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="137" t="s">
+      <c r="C17" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="137"/>
+      <c r="D17" s="158"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -16511,20 +16544,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="137" t="s">
+      <c r="C18" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="137"/>
+      <c r="D18" s="158"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="157" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="137"/>
+      <c r="D19" s="158"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="112" t="s">
@@ -16607,15 +16640,15 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="174" t="s">
+      <c r="A24" s="154" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="175"/>
-      <c r="G24" s="176"/>
+      <c r="B24" s="155"/>
+      <c r="C24" s="155"/>
+      <c r="D24" s="155"/>
+      <c r="E24" s="155"/>
+      <c r="F24" s="155"/>
+      <c r="G24" s="156"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="91" t="s">
@@ -16659,28 +16692,28 @@
       <c r="C28"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="173" t="s">
+      <c r="A29" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="173"/>
-      <c r="D29" s="173"/>
-      <c r="E29" s="173"/>
-      <c r="F29" s="173"/>
-      <c r="G29" s="173"/>
+      <c r="B29" s="133"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="133"/>
+      <c r="E29" s="133"/>
+      <c r="F29" s="133"/>
+      <c r="G29" s="133"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="168"/>
-      <c r="D30" s="168"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="169"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="136"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="95"/>
@@ -16698,12 +16731,12 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="106"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="152"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="164"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31" s="102"/>
@@ -16721,12 +16754,12 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="107"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="154"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="165"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -16744,12 +16777,12 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="108"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="156"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="166"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -16769,28 +16802,28 @@
       <c r="C34"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="170" t="s">
+      <c r="A35" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B35" s="171"/>
-      <c r="C35" s="171"/>
-      <c r="D35" s="171"/>
-      <c r="E35" s="171"/>
-      <c r="F35" s="171"/>
-      <c r="G35" s="172"/>
+      <c r="B35" s="152"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="153"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="148" t="s">
+      <c r="B36" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="148"/>
-      <c r="D36" s="148"/>
-      <c r="E36" s="148"/>
-      <c r="F36" s="148"/>
-      <c r="G36" s="148"/>
+      <c r="C36" s="171"/>
+      <c r="D36" s="171"/>
+      <c r="E36" s="171"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="171"/>
       <c r="H36" s="95"/>
       <c r="I36" s="95"/>
       <c r="J36" s="95"/>
@@ -16810,14 +16843,14 @@
       <c r="A37" s="106">
         <v>1</v>
       </c>
-      <c r="B37" s="149" t="s">
+      <c r="B37" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="149"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="137"/>
       <c r="H37" s="102"/>
       <c r="I37" s="102"/>
       <c r="J37" s="102"/>
@@ -16835,12 +16868,12 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="107"/>
-      <c r="B38" s="150"/>
-      <c r="C38" s="150"/>
-      <c r="D38" s="150"/>
-      <c r="E38" s="150"/>
-      <c r="F38" s="150"/>
-      <c r="G38" s="150"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="138"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -16858,12 +16891,12 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="108"/>
-      <c r="B39" s="151"/>
-      <c r="C39" s="151"/>
-      <c r="D39" s="151"/>
-      <c r="E39" s="151"/>
-      <c r="F39" s="151"/>
-      <c r="G39" s="151"/>
+      <c r="B39" s="139"/>
+      <c r="C39" s="139"/>
+      <c r="D39" s="139"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -16902,28 +16935,28 @@
       <c r="T40"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="170" t="s">
+      <c r="A41" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="171"/>
-      <c r="C41" s="171"/>
-      <c r="D41" s="171"/>
-      <c r="E41" s="171"/>
-      <c r="F41" s="171"/>
-      <c r="G41" s="172"/>
+      <c r="B41" s="152"/>
+      <c r="C41" s="152"/>
+      <c r="D41" s="152"/>
+      <c r="E41" s="152"/>
+      <c r="F41" s="152"/>
+      <c r="G41" s="153"/>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="148" t="s">
+      <c r="B42" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="148"/>
-      <c r="D42" s="148"/>
-      <c r="E42" s="148"/>
-      <c r="F42" s="148"/>
-      <c r="G42" s="148"/>
+      <c r="C42" s="171"/>
+      <c r="D42" s="171"/>
+      <c r="E42" s="171"/>
+      <c r="F42" s="171"/>
+      <c r="G42" s="171"/>
       <c r="H42" s="95"/>
       <c r="I42" s="95"/>
       <c r="J42" s="95"/>
@@ -16941,12 +16974,12 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="106"/>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
-      <c r="F43" s="152"/>
-      <c r="G43" s="153"/>
+      <c r="B43" s="164"/>
+      <c r="C43" s="164"/>
+      <c r="D43" s="164"/>
+      <c r="E43" s="164"/>
+      <c r="F43" s="164"/>
+      <c r="G43" s="172"/>
       <c r="H43" s="102"/>
       <c r="I43" s="102"/>
       <c r="J43" s="102"/>
@@ -16964,12 +16997,12 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="107"/>
-      <c r="B44" s="154"/>
-      <c r="C44" s="154"/>
-      <c r="D44" s="154"/>
-      <c r="E44" s="154"/>
-      <c r="F44" s="154"/>
-      <c r="G44" s="155"/>
+      <c r="B44" s="165"/>
+      <c r="C44" s="165"/>
+      <c r="D44" s="165"/>
+      <c r="E44" s="165"/>
+      <c r="F44" s="165"/>
+      <c r="G44" s="173"/>
       <c r="H44" s="102"/>
       <c r="I44" s="102"/>
       <c r="J44" s="102"/>
@@ -16987,12 +17020,12 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="108"/>
-      <c r="B45" s="156"/>
-      <c r="C45" s="156"/>
-      <c r="D45" s="156"/>
-      <c r="E45" s="156"/>
-      <c r="F45" s="156"/>
-      <c r="G45" s="157"/>
+      <c r="B45" s="166"/>
+      <c r="C45" s="166"/>
+      <c r="D45" s="166"/>
+      <c r="E45" s="166"/>
+      <c r="F45" s="166"/>
+      <c r="G45" s="174"/>
       <c r="H45" s="102"/>
       <c r="I45" s="102"/>
       <c r="J45" s="102"/>
@@ -17068,16 +17101,16 @@
       <c r="B49" s="180" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="186" t="s">
+      <c r="C49" s="182" t="s">
         <v>1</v>
       </c>
       <c r="D49" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="184" t="s">
+      <c r="E49" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="184" t="s">
+      <c r="F49" s="185" t="s">
         <v>170</v>
       </c>
       <c r="G49" s="180" t="s">
@@ -17089,13 +17122,13 @@
       <c r="I49" s="180" t="s">
         <v>236</v>
       </c>
-      <c r="J49" s="184" t="s">
+      <c r="J49" s="185" t="s">
         <v>237</v>
       </c>
-      <c r="K49" s="184" t="s">
+      <c r="K49" s="185" t="s">
         <v>207</v>
       </c>
-      <c r="L49" s="183" t="s">
+      <c r="L49" s="188" t="s">
         <v>224</v>
       </c>
       <c r="M49" s="180" t="s">
@@ -17107,14 +17140,14 @@
       <c r="O49" s="180" t="s">
         <v>189</v>
       </c>
-      <c r="P49" s="187" t="s">
+      <c r="P49" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="Q49" s="188"/>
-      <c r="R49" s="187" t="s">
+      <c r="Q49" s="184"/>
+      <c r="R49" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="S49" s="188"/>
+      <c r="S49" s="184"/>
       <c r="T49" s="32" t="s">
         <v>69</v>
       </c>
@@ -17123,21 +17156,21 @@
       </c>
     </row>
     <row r="50" spans="1:21">
-      <c r="A50" s="182"/>
-      <c r="B50" s="182"/>
-      <c r="C50" s="182"/>
-      <c r="D50" s="182"/>
-      <c r="E50" s="185"/>
-      <c r="F50" s="185"/>
-      <c r="G50" s="182"/>
-      <c r="H50" s="182"/>
-      <c r="I50" s="182"/>
-      <c r="J50" s="185"/>
-      <c r="K50" s="185"/>
-      <c r="L50" s="181"/>
-      <c r="M50" s="182"/>
-      <c r="N50" s="182"/>
-      <c r="O50" s="181"/>
+      <c r="A50" s="181"/>
+      <c r="B50" s="181"/>
+      <c r="C50" s="181"/>
+      <c r="D50" s="181"/>
+      <c r="E50" s="186"/>
+      <c r="F50" s="186"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="181"/>
+      <c r="I50" s="181"/>
+      <c r="J50" s="186"/>
+      <c r="K50" s="186"/>
+      <c r="L50" s="187"/>
+      <c r="M50" s="181"/>
+      <c r="N50" s="181"/>
+      <c r="O50" s="187"/>
       <c r="P50" s="27" t="s">
         <v>74</v>
       </c>
@@ -17153,7 +17186,7 @@
       <c r="T50" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U50" s="182"/>
+      <c r="U50" s="181"/>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="7">
@@ -17805,6 +17838,30 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="U49:U50"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H49:H50"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="O49:O50"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="E49:E50"/>
     <mergeCell ref="B38:G38"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
@@ -17818,30 +17875,6 @@
     <mergeCell ref="B36:G36"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="U49:U50"/>
-    <mergeCell ref="G49:G50"/>
-    <mergeCell ref="H49:H50"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="O49:O50"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="R49:S49"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -18029,10 +18062,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="158" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="137"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -18042,10 +18075,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="137" t="s">
+      <c r="C14" s="158" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="137"/>
+      <c r="D14" s="158"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -18071,28 +18104,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="173" t="s">
+      <c r="A17" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="173"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="173"/>
-      <c r="G17" s="173"/>
+      <c r="B17" s="133"/>
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="133"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="167" t="s">
+      <c r="B18" s="134" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="168"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="169"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="136"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -18104,12 +18137,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="G19" s="152"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="164"/>
+      <c r="G19" s="164"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -18121,12 +18154,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="154"/>
-      <c r="C20" s="154"/>
-      <c r="D20" s="154"/>
-      <c r="E20" s="154"/>
-      <c r="F20" s="154"/>
-      <c r="G20" s="154"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -18138,12 +18171,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
+      <c r="B21" s="166"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="166"/>
+      <c r="F21" s="166"/>
+      <c r="G21" s="166"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -18159,29 +18192,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="170" t="s">
+      <c r="A23" s="151" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="171"/>
-      <c r="C23" s="171"/>
-      <c r="D23" s="171"/>
-      <c r="E23" s="171"/>
-      <c r="F23" s="171"/>
-      <c r="G23" s="172"/>
+      <c r="B23" s="152"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="153"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="148" t="s">
+      <c r="B24" s="171" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="171"/>
+      <c r="F24" s="171"/>
+      <c r="G24" s="171"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -18196,14 +18229,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="149" t="s">
+      <c r="B25" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="149"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="149"/>
-      <c r="F25" s="149"/>
-      <c r="G25" s="149"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -18215,12 +18248,12 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="107"/>
-      <c r="B26" s="150"/>
-      <c r="C26" s="150"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -18232,12 +18265,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="151"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
+      <c r="B27" s="139"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="139"/>
+      <c r="F27" s="139"/>
+      <c r="G27" s="139"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -18266,29 +18299,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="170" t="s">
+      <c r="A29" s="151" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="171"/>
-      <c r="C29" s="171"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="171"/>
-      <c r="F29" s="171"/>
-      <c r="G29" s="172"/>
+      <c r="B29" s="152"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="153"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="148" t="s">
+      <c r="B30" s="171" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="148"/>
-      <c r="D30" s="148"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
-      <c r="G30" s="148"/>
+      <c r="C30" s="171"/>
+      <c r="D30" s="171"/>
+      <c r="E30" s="171"/>
+      <c r="F30" s="171"/>
+      <c r="G30" s="171"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -18301,12 +18334,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="164"/>
+      <c r="D31" s="164"/>
+      <c r="E31" s="164"/>
+      <c r="F31" s="164"/>
+      <c r="G31" s="172"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -18319,12 +18352,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="154"/>
-      <c r="C32" s="154"/>
-      <c r="D32" s="154"/>
-      <c r="E32" s="154"/>
-      <c r="F32" s="154"/>
-      <c r="G32" s="155"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="165"/>
+      <c r="E32" s="165"/>
+      <c r="F32" s="165"/>
+      <c r="G32" s="173"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -18336,12 +18369,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="156"/>
-      <c r="C33" s="156"/>
-      <c r="D33" s="156"/>
-      <c r="E33" s="156"/>
-      <c r="F33" s="156"/>
-      <c r="G33" s="157"/>
+      <c r="B33" s="166"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="166"/>
+      <c r="F33" s="166"/>
+      <c r="G33" s="174"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -18394,31 +18427,31 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="184" t="s">
+      <c r="A37" s="185" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="184" t="s">
+      <c r="B37" s="185" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="184" t="s">
+      <c r="D37" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="184" t="s">
+      <c r="E37" s="185" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="184" t="s">
+      <c r="F37" s="185" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="184" t="s">
+      <c r="G37" s="185" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="184" t="s">
+      <c r="H37" s="185" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="184" t="s">
+      <c r="I37" s="185" t="s">
         <v>229</v>
       </c>
       <c r="J37" s="180" t="s">
@@ -18435,23 +18468,23 @@
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="184" t="s">
+      <c r="P37" s="185" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="193"/>
-      <c r="B38" s="193"/>
+      <c r="A38" s="189"/>
+      <c r="B38" s="189"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="193"/>
-      <c r="E38" s="185"/>
-      <c r="F38" s="185"/>
-      <c r="G38" s="193"/>
-      <c r="H38" s="193"/>
-      <c r="I38" s="193"/>
-      <c r="J38" s="181"/>
+      <c r="D38" s="189"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="186"/>
+      <c r="G38" s="189"/>
+      <c r="H38" s="189"/>
+      <c r="I38" s="189"/>
+      <c r="J38" s="187"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -18467,7 +18500,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="193"/>
+      <c r="P38" s="189"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
@@ -18965,6 +18998,23 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
@@ -18977,23 +19027,6 @@
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B26:G26"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="3">

--- a/meta/plainApi/BlancoApiPlainSample.xlsx
+++ b/meta/plainApi/BlancoApiPlainSample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tueda/data/webstorm/blanco/blancoRestGeneratorKt/meta/plainApi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B033B0-62E8-DF4D-9FF3-E495F7DCFE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7171B4D6-A27E-E342-BC9D-DCE5D552FD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12760" yWindow="4400" windowWidth="29440" windowHeight="20500" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12760" yWindow="4400" windowWidth="29440" windowHeight="20500" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="process" sheetId="19" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="274">
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
@@ -2648,6 +2648,108 @@
     <rPh sb="16" eb="18">
       <t xml:space="preserve">タイオウ </t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>@Consumes(MediaType.ALL)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>追加パス</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ツイカ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Pathクエリ書式</t>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ショシキ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※ processシートで指定されたロケーション+WebサービスIDの後ろに追加されます, 電文定義より優先されます。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※ processシートで指定されたロケーション+WebサービスID+追加パスの後ろに追加されます, 電文定義より優先されます。</t>
+    <rPh sb="51" eb="55">
+      <t xml:space="preserve">デンブンテイギ </t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t xml:space="preserve">ユウセｎ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>/foo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>io.micronaut.http.annotation.Consumes</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>電文処理定義(Kt)・メソッド情報</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">デンブンショリ </t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">テイギ </t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t xml:space="preserve">ジョウホウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※ メソッド種別は自動的に付与されます</t>
+    <rPh sb="6" eb="8">
+      <t xml:space="preserve">シュベツ </t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t xml:space="preserve">ジドウテキニ </t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t xml:space="preserve">フヨ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>/hoge</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>※ 電文処理メソッドに関する諸定義（当面の間、plain 形式電文スタイルでのみ有効です）</t>
+    <rPh sb="2" eb="6">
+      <t xml:space="preserve">デンブンショリ </t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t xml:space="preserve">カンスル </t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t xml:space="preserve">ショテイギ </t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t xml:space="preserve">トウメｎ </t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t xml:space="preserve">アイダ </t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t xml:space="preserve">ケイシキ </t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t xml:space="preserve">デンブｎ </t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t xml:space="preserve">ユウコウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>/bar/{field_2}/{get_sample}</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3576,7 +3678,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3836,6 +3938,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3897,15 +4011,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4564,7 +4669,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="4.5" style="1" customWidth="1"/>
@@ -4605,152 +4710,152 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="169" t="s">
+      <c r="A5" s="170" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="177" t="s">
+      <c r="A6" s="178" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="178"/>
-      <c r="C6" s="179"/>
-      <c r="D6" s="175" t="s">
+      <c r="B6" s="179"/>
+      <c r="C6" s="180"/>
+      <c r="D6" s="176" t="s">
         <v>233</v>
       </c>
-      <c r="E6" s="175"/>
+      <c r="E6" s="176"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="169" t="s">
+      <c r="A7" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="175" t="s">
+      <c r="B7" s="170"/>
+      <c r="C7" s="170"/>
+      <c r="D7" s="176" t="s">
         <v>160</v>
       </c>
-      <c r="E7" s="175"/>
+      <c r="E7" s="176"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="169" t="s">
+      <c r="A8" s="170" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="169"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="175" t="s">
+      <c r="B8" s="170"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="176" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="175"/>
+      <c r="E8" s="176"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="169" t="s">
+      <c r="A9" s="170" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="169"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="175" t="s">
+      <c r="B9" s="170"/>
+      <c r="C9" s="170"/>
+      <c r="D9" s="176" t="s">
         <v>98</v>
       </c>
-      <c r="E9" s="175"/>
+      <c r="E9" s="176"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="169" t="s">
+      <c r="A10" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="175"/>
-      <c r="E10" s="175"/>
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="176"/>
+      <c r="E10" s="176"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="169" t="s">
+      <c r="A11" s="170" t="s">
         <v>97</v>
       </c>
-      <c r="B11" s="169"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="175" t="s">
+      <c r="B11" s="170"/>
+      <c r="C11" s="170"/>
+      <c r="D11" s="176" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="175"/>
+      <c r="E11" s="176"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="149" t="s">
         <v>167</v>
       </c>
-      <c r="B12" s="145"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="158" t="s">
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="E12" s="158"/>
+      <c r="E12" s="159"/>
       <c r="F12" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="145" t="s">
+      <c r="A13" s="149" t="s">
         <v>170</v>
       </c>
-      <c r="B13" s="145"/>
-      <c r="C13" s="145"/>
-      <c r="D13" s="157" t="s">
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="158" t="s">
         <v>208</v>
       </c>
-      <c r="E13" s="158"/>
+      <c r="E13" s="159"/>
     </row>
     <row r="14" spans="1:6" ht="55" customHeight="1">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="149" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="145"/>
-      <c r="C14" s="145"/>
-      <c r="D14" s="176" t="s">
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="177" t="s">
         <v>232</v>
       </c>
-      <c r="E14" s="158"/>
+      <c r="E14" s="159"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="149" t="s">
         <v>191</v>
       </c>
-      <c r="B15" s="145"/>
-      <c r="C15" s="145"/>
-      <c r="D15" s="157"/>
-      <c r="E15" s="158"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="159"/>
       <c r="F15" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="145" t="s">
+      <c r="A16" s="149" t="s">
         <v>192</v>
       </c>
-      <c r="B16" s="145"/>
-      <c r="C16" s="145"/>
-      <c r="D16" s="157"/>
-      <c r="E16" s="158"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="158"/>
+      <c r="E16" s="159"/>
       <c r="F16" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="159" t="s">
+      <c r="A17" s="160" t="s">
         <v>139</v>
       </c>
-      <c r="B17" s="160"/>
-      <c r="C17" s="161"/>
+      <c r="B17" s="161"/>
+      <c r="C17" s="162"/>
       <c r="D17" s="104"/>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="146" t="s">
+      <c r="A18" s="150" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="147"/>
-      <c r="C18" s="148"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="152"/>
       <c r="D18" s="90" t="s">
         <v>137</v>
       </c>
@@ -4770,15 +4875,15 @@
       <c r="B19" s="6"/>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="154" t="s">
+      <c r="A20" s="134" t="s">
         <v>181</v>
       </c>
-      <c r="B20" s="155"/>
-      <c r="C20" s="155"/>
-      <c r="D20" s="155"/>
-      <c r="E20" s="155"/>
-      <c r="F20" s="155"/>
-      <c r="G20" s="156"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="136"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="91" t="s">
@@ -4822,28 +4927,28 @@
       <c r="C24"/>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="133" t="s">
+      <c r="A25" s="137" t="s">
         <v>182</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="134" t="s">
+      <c r="B26" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="135"/>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="136"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="140"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="95"/>
@@ -4854,12 +4959,12 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="106"/>
-      <c r="B27" s="164"/>
-      <c r="C27" s="164"/>
-      <c r="D27" s="164"/>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="164"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="165"/>
+      <c r="E27" s="165"/>
+      <c r="F27" s="165"/>
+      <c r="G27" s="165"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -4870,12 +4975,12 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="107"/>
-      <c r="B28" s="165"/>
-      <c r="C28" s="165"/>
-      <c r="D28" s="165"/>
-      <c r="E28" s="165"/>
-      <c r="F28" s="165"/>
-      <c r="G28" s="165"/>
+      <c r="B28" s="166"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="166"/>
+      <c r="F28" s="166"/>
+      <c r="G28" s="166"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -4886,12 +4991,12 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="108"/>
-      <c r="B29" s="166"/>
-      <c r="C29" s="166"/>
-      <c r="D29" s="166"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="166"/>
-      <c r="G29" s="166"/>
+      <c r="B29" s="167"/>
+      <c r="C29" s="167"/>
+      <c r="D29" s="167"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="167"/>
+      <c r="G29" s="167"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="102"/>
@@ -4923,28 +5028,28 @@
       <c r="C31"/>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="133" t="s">
+      <c r="A32" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="133"/>
-      <c r="C32" s="133"/>
-      <c r="D32" s="133"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="133"/>
+      <c r="B32" s="137"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B33" s="134" t="s">
+      <c r="B33" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C33" s="135"/>
-      <c r="D33" s="135"/>
-      <c r="E33" s="135"/>
-      <c r="F33" s="135"/>
-      <c r="G33" s="136"/>
+      <c r="C33" s="139"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="140"/>
       <c r="H33" s="95"/>
       <c r="I33" s="95"/>
       <c r="J33" s="95"/>
@@ -4957,14 +5062,14 @@
       <c r="A34" s="106">
         <v>1</v>
       </c>
-      <c r="B34" s="137" t="s">
+      <c r="B34" s="141" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="137"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="137"/>
+      <c r="C34" s="141"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="141"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -4975,12 +5080,12 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="107"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="142"/>
+      <c r="D35" s="142"/>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="142"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="102"/>
@@ -4991,12 +5096,12 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="108"/>
-      <c r="B36" s="139"/>
-      <c r="C36" s="139"/>
-      <c r="D36" s="139"/>
-      <c r="E36" s="139"/>
-      <c r="F36" s="139"/>
-      <c r="G36" s="139"/>
+      <c r="B36" s="143"/>
+      <c r="C36" s="143"/>
+      <c r="D36" s="143"/>
+      <c r="E36" s="143"/>
+      <c r="F36" s="143"/>
+      <c r="G36" s="143"/>
       <c r="H36" s="102"/>
       <c r="I36" s="102"/>
       <c r="J36" s="102"/>
@@ -5009,28 +5114,28 @@
       <c r="C37"/>
     </row>
     <row r="38" spans="1:15">
-      <c r="A38" s="151" t="s">
+      <c r="A38" s="155" t="s">
         <v>183</v>
       </c>
-      <c r="B38" s="152"/>
-      <c r="C38" s="152"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
-      <c r="F38" s="152"/>
-      <c r="G38" s="153"/>
+      <c r="B38" s="156"/>
+      <c r="C38" s="156"/>
+      <c r="D38" s="156"/>
+      <c r="E38" s="156"/>
+      <c r="F38" s="156"/>
+      <c r="G38" s="157"/>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="171" t="s">
+      <c r="B39" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C39" s="171"/>
-      <c r="D39" s="171"/>
-      <c r="E39" s="171"/>
-      <c r="F39" s="171"/>
-      <c r="G39" s="171"/>
+      <c r="C39" s="172"/>
+      <c r="D39" s="172"/>
+      <c r="E39" s="172"/>
+      <c r="F39" s="172"/>
+      <c r="G39" s="172"/>
       <c r="H39" s="95"/>
       <c r="I39" s="95"/>
       <c r="J39" s="95"/>
@@ -5043,14 +5148,14 @@
       <c r="A40" s="106">
         <v>1</v>
       </c>
-      <c r="B40" s="137" t="s">
+      <c r="B40" s="142" t="s">
         <v>178</v>
       </c>
-      <c r="C40" s="137"/>
-      <c r="D40" s="137"/>
-      <c r="E40" s="137"/>
-      <c r="F40" s="137"/>
-      <c r="G40" s="137"/>
+      <c r="C40" s="142"/>
+      <c r="D40" s="142"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -5060,13 +5165,17 @@
       <c r="O40"/>
     </row>
     <row r="41" spans="1:15">
-      <c r="A41" s="107"/>
-      <c r="B41" s="138"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
+      <c r="A41" s="107">
+        <v>2</v>
+      </c>
+      <c r="B41" s="142" t="s">
+        <v>268</v>
+      </c>
+      <c r="C41" s="142"/>
+      <c r="D41" s="142"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
       <c r="H41" s="102"/>
       <c r="I41" s="102"/>
       <c r="J41" s="102"/>
@@ -5076,13 +5185,13 @@
       <c r="O41"/>
     </row>
     <row r="42" spans="1:15">
-      <c r="A42" s="108"/>
-      <c r="B42" s="139"/>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
+      <c r="A42" s="107"/>
+      <c r="B42" s="141"/>
+      <c r="C42" s="141"/>
+      <c r="D42" s="141"/>
+      <c r="E42" s="141"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
       <c r="H42" s="102"/>
       <c r="I42" s="102"/>
       <c r="J42" s="102"/>
@@ -5092,69 +5201,69 @@
       <c r="O42"/>
     </row>
     <row r="43" spans="1:15">
-      <c r="A43"/>
-      <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
-      <c r="I43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
+      <c r="A43" s="108"/>
+      <c r="B43" s="143"/>
+      <c r="C43" s="143"/>
+      <c r="D43" s="143"/>
+      <c r="E43" s="143"/>
+      <c r="F43" s="143"/>
+      <c r="G43" s="143"/>
+      <c r="H43" s="102"/>
+      <c r="I43" s="102"/>
+      <c r="J43" s="102"/>
+      <c r="K43" s="102"/>
       <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
     </row>
     <row r="44" spans="1:15">
-      <c r="A44" s="151" t="s">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="155" t="s">
         <v>184</v>
       </c>
-      <c r="B44" s="152"/>
-      <c r="C44" s="152"/>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
-      <c r="F44" s="152"/>
-      <c r="G44" s="153"/>
-    </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="105" t="s">
+      <c r="B45" s="156"/>
+      <c r="C45" s="156"/>
+      <c r="D45" s="156"/>
+      <c r="E45" s="156"/>
+      <c r="F45" s="156"/>
+      <c r="G45" s="157"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B45" s="171" t="s">
+      <c r="B46" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C45" s="171"/>
-      <c r="D45" s="171"/>
-      <c r="E45" s="171"/>
-      <c r="F45" s="171"/>
-      <c r="G45" s="171"/>
-      <c r="H45" s="95"/>
-      <c r="I45" s="95"/>
-      <c r="J45" s="95"/>
-      <c r="K45" s="95"/>
-      <c r="L45" s="95"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="101"/>
-    </row>
-    <row r="46" spans="1:15">
-      <c r="A46" s="106"/>
-      <c r="B46" s="164"/>
-      <c r="C46" s="164"/>
-      <c r="D46" s="164"/>
-      <c r="E46" s="164"/>
-      <c r="F46" s="164"/>
+      <c r="C46" s="172"/>
+      <c r="D46" s="172"/>
+      <c r="E46" s="172"/>
+      <c r="F46" s="172"/>
       <c r="G46" s="172"/>
-      <c r="H46" s="102"/>
-      <c r="I46" s="102"/>
-      <c r="J46" s="102"/>
-      <c r="K46" s="102"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
+      <c r="H46" s="95"/>
+      <c r="I46" s="95"/>
+      <c r="J46" s="95"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="95"/>
+      <c r="N46" s="101"/>
+      <c r="O46" s="101"/>
     </row>
     <row r="47" spans="1:15">
-      <c r="A47" s="107"/>
+      <c r="A47" s="106"/>
       <c r="B47" s="165"/>
       <c r="C47" s="165"/>
       <c r="D47" s="165"/>
@@ -5170,7 +5279,7 @@
       <c r="O47"/>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="108"/>
+      <c r="A48" s="107"/>
       <c r="B48" s="166"/>
       <c r="C48" s="166"/>
       <c r="D48" s="166"/>
@@ -5186,13 +5295,13 @@
       <c r="O48"/>
     </row>
     <row r="49" spans="1:15">
-      <c r="A49" s="121"/>
-      <c r="B49" s="122"/>
-      <c r="C49" s="122"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="122"/>
-      <c r="F49" s="122"/>
-      <c r="G49" s="123"/>
+      <c r="A49" s="108"/>
+      <c r="B49" s="167"/>
+      <c r="C49" s="167"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="167"/>
+      <c r="F49" s="167"/>
+      <c r="G49" s="175"/>
       <c r="H49" s="102"/>
       <c r="I49" s="102"/>
       <c r="J49" s="102"/>
@@ -5202,69 +5311,63 @@
       <c r="O49"/>
     </row>
     <row r="50" spans="1:15">
-      <c r="A50" s="133" t="s">
+      <c r="A50" s="121"/>
+      <c r="B50" s="122"/>
+      <c r="C50" s="122"/>
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="123"/>
+      <c r="H50" s="102"/>
+      <c r="I50" s="102"/>
+      <c r="J50" s="102"/>
+      <c r="K50" s="102"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="137" t="s">
         <v>204</v>
       </c>
-      <c r="B50" s="133"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="133"/>
-      <c r="E50" s="133"/>
-      <c r="F50" s="133"/>
-      <c r="G50" s="133"/>
-    </row>
-    <row r="51" spans="1:15">
-      <c r="A51" s="105" t="s">
+      <c r="B51" s="137"/>
+      <c r="C51" s="137"/>
+      <c r="D51" s="137"/>
+      <c r="E51" s="137"/>
+      <c r="F51" s="137"/>
+      <c r="G51" s="137"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="105" t="s">
+      <c r="B52" s="105" t="s">
         <v>195</v>
       </c>
-      <c r="C51" s="105" t="s">
+      <c r="C52" s="105" t="s">
         <v>196</v>
       </c>
-      <c r="D51" s="105"/>
-      <c r="E51" s="105"/>
-      <c r="F51" s="105"/>
-      <c r="G51" s="105"/>
-      <c r="H51" s="95"/>
-      <c r="I51" s="95"/>
-      <c r="J51" s="95"/>
-      <c r="K51" s="95"/>
-      <c r="L51" s="95"/>
-      <c r="N51" s="101"/>
-      <c r="O51" s="101"/>
-    </row>
-    <row r="52" spans="1:15">
-      <c r="A52" s="106">
+      <c r="D52" s="105"/>
+      <c r="E52" s="105"/>
+      <c r="F52" s="105"/>
+      <c r="G52" s="105"/>
+      <c r="H52" s="95"/>
+      <c r="I52" s="95"/>
+      <c r="J52" s="95"/>
+      <c r="K52" s="95"/>
+      <c r="L52" s="95"/>
+      <c r="N52" s="101"/>
+      <c r="O52" s="101"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="106">
         <v>1</v>
       </c>
-      <c r="B52" s="120" t="s">
+      <c r="B53" s="120" t="s">
         <v>203</v>
       </c>
-      <c r="C52" s="120" t="s">
+      <c r="C53" s="120" t="s">
         <v>197</v>
-      </c>
-      <c r="D52" s="120"/>
-      <c r="E52" s="120"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="120"/>
-      <c r="H52" s="102"/>
-      <c r="I52" s="102"/>
-      <c r="J52" s="102"/>
-      <c r="K52" s="102"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-    </row>
-    <row r="53" spans="1:15">
-      <c r="A53" s="107">
-        <v>2</v>
-      </c>
-      <c r="B53" s="120" t="s">
-        <v>198</v>
-      </c>
-      <c r="C53" s="120" t="s">
-        <v>200</v>
       </c>
       <c r="D53" s="120"/>
       <c r="E53" s="120"/>
@@ -5279,11 +5382,11 @@
       <c r="O53"/>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="108">
-        <v>3</v>
+      <c r="A54" s="107">
+        <v>2</v>
       </c>
       <c r="B54" s="120" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C54" s="120" t="s">
         <v>200</v>
@@ -5301,246 +5404,631 @@
       <c r="O54"/>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55"/>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
+      <c r="A55" s="108">
+        <v>3</v>
+      </c>
+      <c r="B55" s="120" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" s="120" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="120"/>
+      <c r="H55" s="102"/>
+      <c r="I55" s="102"/>
+      <c r="J55" s="102"/>
+      <c r="K55" s="102"/>
       <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
     </row>
     <row r="56" spans="1:15">
-      <c r="A56" s="4" t="s">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="B58" s="135"/>
+      <c r="C58" s="135"/>
+      <c r="D58" s="135"/>
+      <c r="E58" s="135"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136"/>
+      <c r="H58" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="100"/>
+      <c r="C59" s="92"/>
+      <c r="D59" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E59" s="93"/>
+      <c r="F59" s="93"/>
+      <c r="G59" s="94"/>
+      <c r="H59" s="95"/>
+      <c r="I59" s="95"/>
+      <c r="J59" s="95"/>
+      <c r="K59" s="95"/>
+      <c r="L59" s="95"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" s="100"/>
+      <c r="C60" s="92"/>
+      <c r="D60" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="93"/>
+      <c r="F60" s="93"/>
+      <c r="G60" s="94"/>
+      <c r="H60" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I60" s="95"/>
+      <c r="J60" s="95"/>
+      <c r="K60" s="95"/>
+      <c r="L60" s="95"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B61" s="103"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="87"/>
+      <c r="F61" s="87"/>
+      <c r="G61" s="96"/>
+      <c r="H61" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B62" s="103"/>
+      <c r="C62" s="89"/>
+      <c r="D62" s="97"/>
+      <c r="E62" s="98"/>
+      <c r="F62" s="98"/>
+      <c r="G62" s="99"/>
+      <c r="H62" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="C63"/>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="C64"/>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="135"/>
+      <c r="C65" s="135"/>
+      <c r="D65" s="135"/>
+      <c r="E65" s="135"/>
+      <c r="F65" s="135"/>
+      <c r="G65" s="136"/>
+      <c r="H65" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="100"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="133" t="s">
+        <v>235</v>
+      </c>
+      <c r="E66" s="93"/>
+      <c r="F66" s="93"/>
+      <c r="G66" s="94"/>
+      <c r="H66" s="95"/>
+      <c r="I66" s="95"/>
+      <c r="J66" s="95"/>
+      <c r="K66" s="95"/>
+      <c r="L66" s="95"/>
+    </row>
+    <row r="67" spans="1:12">
+      <c r="A67" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B67" s="100"/>
+      <c r="C67" s="92"/>
+      <c r="D67" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="E67" s="93"/>
+      <c r="F67" s="93"/>
+      <c r="G67" s="94"/>
+      <c r="H67" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I67" s="95"/>
+      <c r="J67" s="95"/>
+      <c r="K67" s="95"/>
+      <c r="L67" s="95"/>
+    </row>
+    <row r="68" spans="1:12">
+      <c r="A68" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B68" s="103"/>
+      <c r="C68" s="89"/>
+      <c r="D68" s="86" t="s">
+        <v>271</v>
+      </c>
+      <c r="E68" s="87"/>
+      <c r="F68" s="87"/>
+      <c r="G68" s="96"/>
+      <c r="H68" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
+      <c r="A69" s="88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B69" s="103"/>
+      <c r="C69" s="89"/>
+      <c r="D69" s="97" t="s">
+        <v>273</v>
+      </c>
+      <c r="E69" s="98"/>
+      <c r="F69" s="98"/>
+      <c r="G69" s="99"/>
+      <c r="H69" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
+      <c r="C70"/>
+    </row>
+    <row r="71" spans="1:12">
+      <c r="C71"/>
+    </row>
+    <row r="72" spans="1:12">
+      <c r="A72" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" s="135"/>
+      <c r="C72" s="135"/>
+      <c r="D72" s="135"/>
+      <c r="E72" s="135"/>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136"/>
+      <c r="H72" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="100"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="133" t="s">
+        <v>244</v>
+      </c>
+      <c r="E73" s="93"/>
+      <c r="F73" s="93"/>
+      <c r="G73" s="94"/>
+      <c r="H73" s="95"/>
+      <c r="I73" s="95"/>
+      <c r="J73" s="95"/>
+      <c r="K73" s="95"/>
+      <c r="L73" s="95"/>
+    </row>
+    <row r="74" spans="1:12">
+      <c r="A74" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" s="100"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="E74" s="93"/>
+      <c r="F74" s="93"/>
+      <c r="G74" s="94"/>
+      <c r="H74" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I74" s="95"/>
+      <c r="J74" s="95"/>
+      <c r="K74" s="95"/>
+      <c r="L74" s="95"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75" s="103"/>
+      <c r="C75" s="89"/>
+      <c r="D75" s="86"/>
+      <c r="E75" s="87"/>
+      <c r="F75" s="87"/>
+      <c r="G75" s="96"/>
+      <c r="H75" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
+      <c r="A76" s="88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76" s="103"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="97"/>
+      <c r="E76" s="98"/>
+      <c r="F76" s="98"/>
+      <c r="G76" s="99"/>
+      <c r="H76" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
+      <c r="C77"/>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="1:12">
+      <c r="A79" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="B79" s="135"/>
+      <c r="C79" s="135"/>
+      <c r="D79" s="135"/>
+      <c r="E79" s="135"/>
+      <c r="F79" s="135"/>
+      <c r="G79" s="136"/>
+      <c r="H79" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="B80" s="100"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="133" t="s">
+        <v>245</v>
+      </c>
+      <c r="E80" s="93"/>
+      <c r="F80" s="93"/>
+      <c r="G80" s="94"/>
+      <c r="H80" s="95"/>
+      <c r="I80" s="95"/>
+      <c r="J80" s="95"/>
+      <c r="K80" s="95"/>
+      <c r="L80" s="95"/>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="100"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="E81" s="93"/>
+      <c r="F81" s="93"/>
+      <c r="G81" s="94"/>
+      <c r="H81" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="I81" s="95"/>
+      <c r="J81" s="95"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="95"/>
+    </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="88" t="s">
+        <v>263</v>
+      </c>
+      <c r="B82" s="103"/>
+      <c r="C82" s="89"/>
+      <c r="D82" s="86"/>
+      <c r="E82" s="87"/>
+      <c r="F82" s="87"/>
+      <c r="G82" s="96"/>
+      <c r="H82" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B83" s="103"/>
+      <c r="C83" s="89"/>
+      <c r="D83" s="97"/>
+      <c r="E83" s="98"/>
+      <c r="F83" s="98"/>
+      <c r="G83" s="99"/>
+      <c r="H83" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
+      <c r="C84"/>
+    </row>
+    <row r="85" spans="1:12">
+      <c r="C85"/>
+    </row>
+    <row r="86" spans="1:12">
+      <c r="A86" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="5"/>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" s="142" t="s">
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="5"/>
+    </row>
+    <row r="87" spans="1:12">
+      <c r="A87" s="146" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="144"/>
-      <c r="C57" s="142" t="s">
+      <c r="B87" s="148"/>
+      <c r="C87" s="146" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="143"/>
-      <c r="E57" s="144"/>
-      <c r="F57" s="27" t="s">
+      <c r="D87" s="147"/>
+      <c r="E87" s="148"/>
+      <c r="F87" s="27" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
-      <c r="A58" s="149"/>
-      <c r="B58" s="150"/>
-      <c r="C58" s="149"/>
-      <c r="D58" s="167"/>
-      <c r="E58" s="150"/>
-      <c r="F58" s="43"/>
-    </row>
-    <row r="59" spans="1:15">
-      <c r="A59" s="140"/>
-      <c r="B59" s="141"/>
-      <c r="C59" s="140"/>
-      <c r="D59" s="168"/>
-      <c r="E59" s="141"/>
-      <c r="F59" s="43"/>
-    </row>
-    <row r="60" spans="1:15">
-      <c r="A60" s="140"/>
-      <c r="B60" s="141"/>
-      <c r="C60" s="140"/>
-      <c r="D60" s="168"/>
-      <c r="E60" s="141"/>
-      <c r="F60" s="43"/>
-    </row>
-    <row r="61" spans="1:15">
-      <c r="A61" s="140"/>
-      <c r="B61" s="141"/>
-      <c r="C61" s="140"/>
-      <c r="D61" s="168"/>
-      <c r="E61" s="141"/>
-      <c r="F61" s="43"/>
-    </row>
-    <row r="62" spans="1:15">
-      <c r="A62" s="140"/>
-      <c r="B62" s="141"/>
-      <c r="C62" s="140"/>
-      <c r="D62" s="168"/>
-      <c r="E62" s="141"/>
-      <c r="F62" s="43"/>
-    </row>
-    <row r="63" spans="1:15">
-      <c r="A63" s="140"/>
-      <c r="B63" s="141"/>
-      <c r="C63" s="140"/>
-      <c r="D63" s="168"/>
-      <c r="E63" s="141"/>
-      <c r="F63" s="43"/>
-    </row>
-    <row r="64" spans="1:15">
-      <c r="A64" s="140"/>
-      <c r="B64" s="141"/>
-      <c r="C64" s="140"/>
-      <c r="D64" s="168"/>
-      <c r="E64" s="141"/>
-      <c r="F64" s="43"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="140"/>
-      <c r="B65" s="141"/>
-      <c r="C65" s="140"/>
-      <c r="D65" s="168"/>
-      <c r="E65" s="141"/>
-      <c r="F65" s="43"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="140"/>
-      <c r="B66" s="141"/>
-      <c r="C66" s="140"/>
-      <c r="D66" s="168"/>
-      <c r="E66" s="141"/>
-      <c r="F66" s="43"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="140"/>
-      <c r="B67" s="141"/>
-      <c r="C67" s="140"/>
-      <c r="D67" s="168"/>
-      <c r="E67" s="141"/>
-      <c r="F67" s="43"/>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="140"/>
-      <c r="B68" s="141"/>
-      <c r="C68" s="140"/>
-      <c r="D68" s="168"/>
-      <c r="E68" s="141"/>
-      <c r="F68" s="43"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="140"/>
-      <c r="B69" s="141"/>
-      <c r="C69" s="140"/>
-      <c r="D69" s="168"/>
-      <c r="E69" s="141"/>
-      <c r="F69" s="43"/>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="140"/>
-      <c r="B70" s="141"/>
-      <c r="C70" s="140"/>
-      <c r="D70" s="168"/>
-      <c r="E70" s="141"/>
-      <c r="F70" s="43"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="140"/>
-      <c r="B71" s="141"/>
-      <c r="C71" s="140"/>
-      <c r="D71" s="168"/>
-      <c r="E71" s="141"/>
-      <c r="F71" s="43"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="140"/>
-      <c r="B72" s="141"/>
-      <c r="C72" s="140"/>
-      <c r="D72" s="168"/>
-      <c r="E72" s="141"/>
-      <c r="F72" s="43"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="140"/>
-      <c r="B73" s="141"/>
-      <c r="C73" s="140"/>
-      <c r="D73" s="168"/>
-      <c r="E73" s="141"/>
-      <c r="F73" s="43"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="140"/>
-      <c r="B74" s="141"/>
-      <c r="C74" s="140"/>
-      <c r="D74" s="168"/>
-      <c r="E74" s="141"/>
-      <c r="F74" s="43"/>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="140"/>
-      <c r="B75" s="141"/>
-      <c r="C75" s="140"/>
-      <c r="D75" s="168"/>
-      <c r="E75" s="141"/>
-      <c r="F75" s="43"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="140"/>
-      <c r="B76" s="141"/>
-      <c r="C76" s="140"/>
-      <c r="D76" s="168"/>
-      <c r="E76" s="141"/>
-      <c r="F76" s="43"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="140"/>
-      <c r="B77" s="141"/>
-      <c r="C77" s="140"/>
-      <c r="D77" s="168"/>
-      <c r="E77" s="141"/>
-      <c r="F77" s="43"/>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78" s="140"/>
-      <c r="B78" s="141"/>
-      <c r="C78" s="140"/>
-      <c r="D78" s="168"/>
-      <c r="E78" s="141"/>
-      <c r="F78" s="43"/>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="140"/>
-      <c r="B79" s="141"/>
-      <c r="C79" s="140"/>
-      <c r="D79" s="168"/>
-      <c r="E79" s="141"/>
-      <c r="F79" s="43"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="140"/>
-      <c r="B80" s="141"/>
-      <c r="C80" s="140"/>
-      <c r="D80" s="168"/>
-      <c r="E80" s="141"/>
-      <c r="F80" s="43"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="140"/>
-      <c r="B81" s="141"/>
-      <c r="C81" s="140"/>
-      <c r="D81" s="168"/>
-      <c r="E81" s="141"/>
-      <c r="F81" s="43"/>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="162"/>
-      <c r="B82" s="163"/>
-      <c r="C82" s="162"/>
-      <c r="D82" s="170"/>
-      <c r="E82" s="163"/>
-      <c r="F82" s="44"/>
+    <row r="88" spans="1:12">
+      <c r="A88" s="153"/>
+      <c r="B88" s="154"/>
+      <c r="C88" s="153"/>
+      <c r="D88" s="168"/>
+      <c r="E88" s="154"/>
+      <c r="F88" s="43"/>
+    </row>
+    <row r="89" spans="1:12">
+      <c r="A89" s="144"/>
+      <c r="B89" s="145"/>
+      <c r="C89" s="144"/>
+      <c r="D89" s="169"/>
+      <c r="E89" s="145"/>
+      <c r="F89" s="43"/>
+    </row>
+    <row r="90" spans="1:12">
+      <c r="A90" s="144"/>
+      <c r="B90" s="145"/>
+      <c r="C90" s="144"/>
+      <c r="D90" s="169"/>
+      <c r="E90" s="145"/>
+      <c r="F90" s="43"/>
+    </row>
+    <row r="91" spans="1:12">
+      <c r="A91" s="144"/>
+      <c r="B91" s="145"/>
+      <c r="C91" s="144"/>
+      <c r="D91" s="169"/>
+      <c r="E91" s="145"/>
+      <c r="F91" s="43"/>
+    </row>
+    <row r="92" spans="1:12">
+      <c r="A92" s="144"/>
+      <c r="B92" s="145"/>
+      <c r="C92" s="144"/>
+      <c r="D92" s="169"/>
+      <c r="E92" s="145"/>
+      <c r="F92" s="43"/>
+    </row>
+    <row r="93" spans="1:12">
+      <c r="A93" s="144"/>
+      <c r="B93" s="145"/>
+      <c r="C93" s="144"/>
+      <c r="D93" s="169"/>
+      <c r="E93" s="145"/>
+      <c r="F93" s="43"/>
+    </row>
+    <row r="94" spans="1:12">
+      <c r="A94" s="144"/>
+      <c r="B94" s="145"/>
+      <c r="C94" s="144"/>
+      <c r="D94" s="169"/>
+      <c r="E94" s="145"/>
+      <c r="F94" s="43"/>
+    </row>
+    <row r="95" spans="1:12">
+      <c r="A95" s="144"/>
+      <c r="B95" s="145"/>
+      <c r="C95" s="144"/>
+      <c r="D95" s="169"/>
+      <c r="E95" s="145"/>
+      <c r="F95" s="43"/>
+    </row>
+    <row r="96" spans="1:12">
+      <c r="A96" s="144"/>
+      <c r="B96" s="145"/>
+      <c r="C96" s="144"/>
+      <c r="D96" s="169"/>
+      <c r="E96" s="145"/>
+      <c r="F96" s="43"/>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="144"/>
+      <c r="B97" s="145"/>
+      <c r="C97" s="144"/>
+      <c r="D97" s="169"/>
+      <c r="E97" s="145"/>
+      <c r="F97" s="43"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="144"/>
+      <c r="B98" s="145"/>
+      <c r="C98" s="144"/>
+      <c r="D98" s="169"/>
+      <c r="E98" s="145"/>
+      <c r="F98" s="43"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="144"/>
+      <c r="B99" s="145"/>
+      <c r="C99" s="144"/>
+      <c r="D99" s="169"/>
+      <c r="E99" s="145"/>
+      <c r="F99" s="43"/>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="144"/>
+      <c r="B100" s="145"/>
+      <c r="C100" s="144"/>
+      <c r="D100" s="169"/>
+      <c r="E100" s="145"/>
+      <c r="F100" s="43"/>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="144"/>
+      <c r="B101" s="145"/>
+      <c r="C101" s="144"/>
+      <c r="D101" s="169"/>
+      <c r="E101" s="145"/>
+      <c r="F101" s="43"/>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="144"/>
+      <c r="B102" s="145"/>
+      <c r="C102" s="144"/>
+      <c r="D102" s="169"/>
+      <c r="E102" s="145"/>
+      <c r="F102" s="43"/>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" s="144"/>
+      <c r="B103" s="145"/>
+      <c r="C103" s="144"/>
+      <c r="D103" s="169"/>
+      <c r="E103" s="145"/>
+      <c r="F103" s="43"/>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="144"/>
+      <c r="B104" s="145"/>
+      <c r="C104" s="144"/>
+      <c r="D104" s="169"/>
+      <c r="E104" s="145"/>
+      <c r="F104" s="43"/>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="144"/>
+      <c r="B105" s="145"/>
+      <c r="C105" s="144"/>
+      <c r="D105" s="169"/>
+      <c r="E105" s="145"/>
+      <c r="F105" s="43"/>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="144"/>
+      <c r="B106" s="145"/>
+      <c r="C106" s="144"/>
+      <c r="D106" s="169"/>
+      <c r="E106" s="145"/>
+      <c r="F106" s="43"/>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="144"/>
+      <c r="B107" s="145"/>
+      <c r="C107" s="144"/>
+      <c r="D107" s="169"/>
+      <c r="E107" s="145"/>
+      <c r="F107" s="43"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="144"/>
+      <c r="B108" s="145"/>
+      <c r="C108" s="144"/>
+      <c r="D108" s="169"/>
+      <c r="E108" s="145"/>
+      <c r="F108" s="43"/>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="144"/>
+      <c r="B109" s="145"/>
+      <c r="C109" s="144"/>
+      <c r="D109" s="169"/>
+      <c r="E109" s="145"/>
+      <c r="F109" s="43"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="144"/>
+      <c r="B110" s="145"/>
+      <c r="C110" s="144"/>
+      <c r="D110" s="169"/>
+      <c r="E110" s="145"/>
+      <c r="F110" s="43"/>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="144"/>
+      <c r="B111" s="145"/>
+      <c r="C111" s="144"/>
+      <c r="D111" s="169"/>
+      <c r="E111" s="145"/>
+      <c r="F111" s="43"/>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="163"/>
+      <c r="B112" s="164"/>
+      <c r="C112" s="163"/>
+      <c r="D112" s="171"/>
+      <c r="E112" s="164"/>
+      <c r="F112" s="44"/>
     </row>
   </sheetData>
-  <mergeCells count="99">
+  <mergeCells count="104">
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="D7:E7"/>
@@ -5557,84 +6045,89 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C112:E112"/>
     <mergeCell ref="B39:G39"/>
     <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B41:G41"/>
     <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B43:G43"/>
     <mergeCell ref="B46:G46"/>
     <mergeCell ref="B47:G47"/>
     <mergeCell ref="B48:G48"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A112:B112"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="B29:G29"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="A104:B104"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A107:B107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C87:E87"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A88:B88"/>
     <mergeCell ref="B26:G26"/>
     <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A67:B67"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="B33:G33"/>
     <mergeCell ref="B34:G34"/>
@@ -5646,7 +6139,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18" xr:uid="{AA005DBF-E840-AD43-AC91-CD6CE016CB50}">
       <formula1>isImport</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C52:C54" xr:uid="{5359E819-3DA9-9F40-8153-6EB281F58DC2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C53:C55" xr:uid="{5359E819-3DA9-9F40-8153-6EB281F58DC2}">
       <formula1>path</formula1>
     </dataValidation>
   </dataValidations>
@@ -5657,12 +6150,18 @@
   </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>config!$B$5:$B$6</xm:f>
           </x14:formula1>
           <xm:sqref>D17</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6C80DF18-3566-F248-8B00-A37C4881F9D8}">
+          <x14:formula1>
+            <xm:f>config!$C$5:$C$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>D59 D66 D73 D80</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5846,10 +6345,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="158" t="s">
+      <c r="C17" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="158"/>
+      <c r="D17" s="159"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -5859,20 +6358,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="158"/>
+      <c r="D18" s="159"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="157" t="s">
+      <c r="C19" s="158" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="158"/>
+      <c r="D19" s="159"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="112" t="s">
@@ -5953,28 +6452,28 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="134" t="s">
+      <c r="B25" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="135"/>
-      <c r="D25" s="135"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="136"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
       <c r="H25" s="95"/>
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
@@ -5991,12 +6490,12 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="106"/>
-      <c r="B26" s="164"/>
-      <c r="C26" s="164"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
-      <c r="G26" s="164"/>
+      <c r="B26" s="165"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="J26" s="102"/>
@@ -6013,12 +6512,12 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="107"/>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-      <c r="F27" s="165"/>
-      <c r="G27" s="165"/>
+      <c r="B27" s="166"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="166"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -6035,12 +6534,12 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="108"/>
-      <c r="B28" s="166"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="166"/>
-      <c r="G28" s="166"/>
+      <c r="B28" s="167"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="167"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -6059,28 +6558,28 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="151" t="s">
+      <c r="A30" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="152"/>
-      <c r="C30" s="152"/>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="153"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156"/>
+      <c r="G30" s="157"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="171" t="s">
+      <c r="B31" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="172"/>
       <c r="H31" s="95"/>
       <c r="I31" s="95"/>
       <c r="J31" s="95"/>
@@ -6099,14 +6598,14 @@
       <c r="A32" s="106">
         <v>1</v>
       </c>
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -6123,12 +6622,12 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="107"/>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
+      <c r="B33" s="142"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -6145,12 +6644,12 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="108"/>
-      <c r="B34" s="139"/>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
+      <c r="B34" s="143"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="143"/>
+      <c r="E34" s="143"/>
+      <c r="F34" s="143"/>
+      <c r="G34" s="143"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -6187,28 +6686,28 @@
       <c r="S35"/>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="151" t="s">
+      <c r="A36" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="152"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
-      <c r="G36" s="153"/>
+      <c r="B36" s="156"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="156"/>
+      <c r="G36" s="157"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="171" t="s">
+      <c r="B37" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="171"/>
-      <c r="D37" s="171"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
+      <c r="C37" s="172"/>
+      <c r="D37" s="172"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
       <c r="H37" s="95"/>
       <c r="I37" s="95"/>
       <c r="J37" s="95"/>
@@ -6225,12 +6724,12 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="106"/>
-      <c r="B38" s="164"/>
-      <c r="C38" s="164"/>
-      <c r="D38" s="164"/>
-      <c r="E38" s="164"/>
-      <c r="F38" s="164"/>
-      <c r="G38" s="172"/>
+      <c r="B38" s="165"/>
+      <c r="C38" s="165"/>
+      <c r="D38" s="165"/>
+      <c r="E38" s="165"/>
+      <c r="F38" s="165"/>
+      <c r="G38" s="173"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -6247,12 +6746,12 @@
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="107"/>
-      <c r="B39" s="165"/>
-      <c r="C39" s="165"/>
-      <c r="D39" s="165"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="165"/>
-      <c r="G39" s="173"/>
+      <c r="B39" s="166"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="174"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -6269,12 +6768,12 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="108"/>
-      <c r="B40" s="166"/>
-      <c r="C40" s="166"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="166"/>
-      <c r="F40" s="166"/>
-      <c r="G40" s="174"/>
+      <c r="B40" s="167"/>
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="175"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -6341,78 +6840,78 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="180" t="s">
+      <c r="A44" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="180" t="s">
+      <c r="B44" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="182" t="s">
+      <c r="C44" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="D44" s="180" t="s">
+      <c r="D44" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="185" t="s">
+      <c r="E44" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F44" s="185" t="s">
+      <c r="F44" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G44" s="180" t="s">
+      <c r="G44" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="180" t="s">
+      <c r="H44" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="180" t="s">
+      <c r="I44" s="181" t="s">
         <v>236</v>
       </c>
-      <c r="J44" s="185" t="s">
+      <c r="J44" s="186" t="s">
         <v>237</v>
       </c>
-      <c r="K44" s="185" t="s">
+      <c r="K44" s="186" t="s">
         <v>207</v>
       </c>
-      <c r="L44" s="188" t="s">
+      <c r="L44" s="189" t="s">
         <v>224</v>
       </c>
-      <c r="M44" s="180" t="s">
+      <c r="M44" s="181" t="s">
         <v>221</v>
       </c>
-      <c r="N44" s="180" t="s">
+      <c r="N44" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="O44" s="183" t="s">
+      <c r="O44" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="P44" s="184"/>
-      <c r="Q44" s="183" t="s">
+      <c r="P44" s="185"/>
+      <c r="Q44" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="R44" s="184"/>
+      <c r="R44" s="185"/>
       <c r="S44" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="T44" s="180" t="s">
+      <c r="T44" s="181" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="181"/>
-      <c r="B45" s="181"/>
-      <c r="C45" s="181"/>
-      <c r="D45" s="181"/>
-      <c r="E45" s="186"/>
-      <c r="F45" s="186"/>
-      <c r="G45" s="181"/>
-      <c r="H45" s="181"/>
-      <c r="I45" s="181"/>
-      <c r="J45" s="186"/>
-      <c r="K45" s="186"/>
-      <c r="L45" s="187"/>
-      <c r="M45" s="181"/>
-      <c r="N45" s="187"/>
+      <c r="A45" s="182"/>
+      <c r="B45" s="182"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="187"/>
+      <c r="F45" s="187"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="182"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="187"/>
+      <c r="K45" s="187"/>
+      <c r="L45" s="188"/>
+      <c r="M45" s="182"/>
+      <c r="N45" s="188"/>
       <c r="O45" s="27" t="s">
         <v>74</v>
       </c>
@@ -6428,7 +6927,7 @@
       <c r="S45" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T45" s="181"/>
+      <c r="T45" s="182"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="7">
@@ -7272,10 +7771,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="158" t="s">
+      <c r="C13" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="158"/>
+      <c r="D13" s="159"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -7285,10 +7784,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="193" t="s">
+      <c r="C14" s="194" t="s">
         <v>240</v>
       </c>
-      <c r="D14" s="158"/>
+      <c r="D14" s="159"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -7314,28 +7813,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="140"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -7347,12 +7846,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -7364,12 +7863,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="165"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
+      <c r="B20" s="166"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="166"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -7381,12 +7880,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="166"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
+      <c r="B21" s="167"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -7402,29 +7901,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="151" t="s">
+      <c r="A23" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="153"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="172"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -7439,14 +7938,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -7460,14 +7959,14 @@
       <c r="A26" s="107">
         <v>2</v>
       </c>
-      <c r="B26" s="138" t="s">
+      <c r="B26" s="142" t="s">
         <v>239</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -7479,12 +7978,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
+      <c r="B27" s="143"/>
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -7513,29 +8012,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="151" t="s">
+      <c r="A29" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="152"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="153"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="157"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="171" t="s">
+      <c r="B30" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="172"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -7548,12 +8047,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="172"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="173"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -7566,12 +8065,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="173"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="174"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -7583,12 +8082,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="174"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="175"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -7641,64 +8140,64 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="185" t="s">
+      <c r="A37" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="185" t="s">
+      <c r="B37" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="185" t="s">
+      <c r="D37" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="185" t="s">
+      <c r="E37" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="185" t="s">
+      <c r="F37" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="185" t="s">
+      <c r="G37" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="185" t="s">
+      <c r="H37" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="185" t="s">
+      <c r="I37" s="186" t="s">
         <v>229</v>
       </c>
-      <c r="J37" s="180" t="s">
+      <c r="J37" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="190" t="s">
+      <c r="K37" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L37" s="191"/>
-      <c r="M37" s="192" t="s">
+      <c r="L37" s="192"/>
+      <c r="M37" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N37" s="191"/>
+      <c r="N37" s="192"/>
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="185" t="s">
+      <c r="P37" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="189"/>
-      <c r="B38" s="189"/>
+      <c r="A38" s="190"/>
+      <c r="B38" s="190"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="189"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="187"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="188"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -7714,7 +8213,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="189"/>
+      <c r="P38" s="190"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
@@ -8889,7 +9388,9 @@
         <v>231</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="46"/>
+      <c r="C13" s="46" t="s">
+        <v>267</v>
+      </c>
       <c r="D13" s="33"/>
       <c r="E13" s="1" t="s">
         <v>230</v>
@@ -8931,10 +9432,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="158" t="s">
+      <c r="C17" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="158"/>
+      <c r="D17" s="159"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -8944,20 +9445,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="158"/>
+      <c r="D18" s="159"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="157" t="s">
+      <c r="C19" s="158" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="158"/>
+      <c r="D19" s="159"/>
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="112" t="s">
@@ -9036,28 +9537,28 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="134" t="s">
+      <c r="B25" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C25" s="135"/>
-      <c r="D25" s="135"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="136"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="140"/>
       <c r="H25" s="95"/>
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
@@ -9074,12 +9575,12 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="106"/>
-      <c r="B26" s="164"/>
-      <c r="C26" s="164"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
-      <c r="G26" s="164"/>
+      <c r="B26" s="165"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="J26" s="102"/>
@@ -9096,12 +9597,12 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="107"/>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-      <c r="F27" s="165"/>
-      <c r="G27" s="165"/>
+      <c r="B27" s="166"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="166"/>
+      <c r="F27" s="166"/>
+      <c r="G27" s="166"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="102"/>
@@ -9118,12 +9619,12 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="108"/>
-      <c r="B28" s="166"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="166"/>
-      <c r="F28" s="166"/>
-      <c r="G28" s="166"/>
+      <c r="B28" s="167"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="167"/>
+      <c r="G28" s="167"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="J28" s="102"/>
@@ -9142,28 +9643,28 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" s="151" t="s">
+      <c r="A30" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="152"/>
-      <c r="C30" s="152"/>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
-      <c r="F30" s="152"/>
-      <c r="G30" s="153"/>
+      <c r="B30" s="156"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="156"/>
+      <c r="E30" s="156"/>
+      <c r="F30" s="156"/>
+      <c r="G30" s="157"/>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="171" t="s">
+      <c r="B31" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="171"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="172"/>
       <c r="H31" s="95"/>
       <c r="I31" s="95"/>
       <c r="J31" s="95"/>
@@ -9182,14 +9683,14 @@
       <c r="A32" s="106">
         <v>1</v>
       </c>
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
+      <c r="C32" s="141"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="141"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -9206,12 +9707,12 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="107"/>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
+      <c r="B33" s="142"/>
+      <c r="C33" s="142"/>
+      <c r="D33" s="142"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -9228,12 +9729,12 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="108"/>
-      <c r="B34" s="139"/>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
+      <c r="B34" s="143"/>
+      <c r="C34" s="143"/>
+      <c r="D34" s="143"/>
+      <c r="E34" s="143"/>
+      <c r="F34" s="143"/>
+      <c r="G34" s="143"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="J34" s="102"/>
@@ -9270,28 +9771,28 @@
       <c r="S35"/>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="151" t="s">
+      <c r="A36" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="152"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
-      <c r="F36" s="152"/>
-      <c r="G36" s="153"/>
+      <c r="B36" s="156"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="156"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="156"/>
+      <c r="G36" s="157"/>
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="171" t="s">
+      <c r="B37" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C37" s="171"/>
-      <c r="D37" s="171"/>
-      <c r="E37" s="171"/>
-      <c r="F37" s="171"/>
-      <c r="G37" s="171"/>
+      <c r="C37" s="172"/>
+      <c r="D37" s="172"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
       <c r="H37" s="95"/>
       <c r="I37" s="95"/>
       <c r="J37" s="95"/>
@@ -9308,12 +9809,12 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" s="106"/>
-      <c r="B38" s="164"/>
-      <c r="C38" s="164"/>
-      <c r="D38" s="164"/>
-      <c r="E38" s="164"/>
-      <c r="F38" s="164"/>
-      <c r="G38" s="172"/>
+      <c r="B38" s="165"/>
+      <c r="C38" s="165"/>
+      <c r="D38" s="165"/>
+      <c r="E38" s="165"/>
+      <c r="F38" s="165"/>
+      <c r="G38" s="173"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -9330,12 +9831,12 @@
     </row>
     <row r="39" spans="1:21">
       <c r="A39" s="107"/>
-      <c r="B39" s="165"/>
-      <c r="C39" s="165"/>
-      <c r="D39" s="165"/>
-      <c r="E39" s="165"/>
-      <c r="F39" s="165"/>
-      <c r="G39" s="173"/>
+      <c r="B39" s="166"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="174"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -9352,12 +9853,12 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" s="108"/>
-      <c r="B40" s="166"/>
-      <c r="C40" s="166"/>
-      <c r="D40" s="166"/>
-      <c r="E40" s="166"/>
-      <c r="F40" s="166"/>
-      <c r="G40" s="174"/>
+      <c r="B40" s="167"/>
+      <c r="C40" s="167"/>
+      <c r="D40" s="167"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="167"/>
+      <c r="G40" s="175"/>
       <c r="H40" s="102"/>
       <c r="I40" s="102"/>
       <c r="J40" s="102"/>
@@ -9424,78 +9925,78 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="180" t="s">
+      <c r="A44" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="180" t="s">
+      <c r="B44" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C44" s="182" t="s">
+      <c r="C44" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="D44" s="180" t="s">
+      <c r="D44" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="185" t="s">
+      <c r="E44" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F44" s="185" t="s">
+      <c r="F44" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G44" s="180" t="s">
+      <c r="G44" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="180" t="s">
+      <c r="H44" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="180" t="s">
+      <c r="I44" s="181" t="s">
         <v>236</v>
       </c>
-      <c r="J44" s="185" t="s">
+      <c r="J44" s="186" t="s">
         <v>237</v>
       </c>
-      <c r="K44" s="185" t="s">
+      <c r="K44" s="186" t="s">
         <v>207</v>
       </c>
-      <c r="L44" s="188" t="s">
+      <c r="L44" s="189" t="s">
         <v>224</v>
       </c>
-      <c r="M44" s="180" t="s">
+      <c r="M44" s="181" t="s">
         <v>221</v>
       </c>
-      <c r="N44" s="180" t="s">
+      <c r="N44" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="O44" s="183" t="s">
+      <c r="O44" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="P44" s="184"/>
-      <c r="Q44" s="183" t="s">
+      <c r="P44" s="185"/>
+      <c r="Q44" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="R44" s="184"/>
+      <c r="R44" s="185"/>
       <c r="S44" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="T44" s="180" t="s">
+      <c r="T44" s="181" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:21">
-      <c r="A45" s="181"/>
-      <c r="B45" s="181"/>
-      <c r="C45" s="181"/>
-      <c r="D45" s="181"/>
-      <c r="E45" s="186"/>
-      <c r="F45" s="186"/>
-      <c r="G45" s="181"/>
-      <c r="H45" s="181"/>
-      <c r="I45" s="181"/>
-      <c r="J45" s="186"/>
-      <c r="K45" s="186"/>
-      <c r="L45" s="187"/>
-      <c r="M45" s="181"/>
-      <c r="N45" s="187"/>
+      <c r="A45" s="182"/>
+      <c r="B45" s="182"/>
+      <c r="C45" s="182"/>
+      <c r="D45" s="182"/>
+      <c r="E45" s="187"/>
+      <c r="F45" s="187"/>
+      <c r="G45" s="182"/>
+      <c r="H45" s="182"/>
+      <c r="I45" s="182"/>
+      <c r="J45" s="187"/>
+      <c r="K45" s="187"/>
+      <c r="L45" s="188"/>
+      <c r="M45" s="182"/>
+      <c r="N45" s="188"/>
       <c r="O45" s="27" t="s">
         <v>74</v>
       </c>
@@ -9511,7 +10012,7 @@
       <c r="S45" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="T45" s="181"/>
+      <c r="T45" s="182"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46" s="7">
@@ -10172,7 +10673,7 @@
     <mergeCell ref="B26:G26"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <dataValidations count="4">
+  <dataValidations disablePrompts="1" count="4">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="C8" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>Validate実装パターン</formula1>
     </dataValidation>
@@ -10194,7 +10695,7 @@
   </headerFooter>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>config!$B$5:$B$6</xm:f>
@@ -10383,10 +10884,10 @@
         <v>167</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="158" t="s">
+      <c r="C15" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="158"/>
+      <c r="D15" s="159"/>
       <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
@@ -10396,10 +10897,10 @@
         <v>170</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="193" t="s">
+      <c r="C16" s="194" t="s">
         <v>240</v>
       </c>
-      <c r="D16" s="158"/>
+      <c r="D16" s="159"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="112" t="s">
@@ -10425,28 +10926,28 @@
       <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="134" t="s">
+      <c r="B20" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="95"/>
       <c r="I20" s="95"/>
       <c r="K20" s="95"/>
@@ -10458,12 +10959,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="106"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="164"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -10475,12 +10976,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="107"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="165"/>
-      <c r="F22" s="165"/>
-      <c r="G22" s="165"/>
+      <c r="B22" s="166"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="K22" s="102"/>
@@ -10492,12 +10993,12 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="108"/>
-      <c r="B23" s="166"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
+      <c r="B23" s="167"/>
+      <c r="C23" s="167"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="102"/>
       <c r="I23" s="102"/>
       <c r="J23" s="95"/>
@@ -10513,29 +11014,29 @@
       <c r="J24" s="102"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="153"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="157"/>
       <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="102"/>
@@ -10550,14 +11051,14 @@
       <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B27" s="137" t="s">
+      <c r="B27" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -10571,14 +11072,14 @@
       <c r="A28" s="107">
         <v>2</v>
       </c>
-      <c r="B28" s="138" t="s">
+      <c r="B28" s="142" t="s">
         <v>239</v>
       </c>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="K28" s="102"/>
@@ -10590,12 +11091,12 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="108"/>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="95"/>
@@ -10624,29 +11125,29 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="151" t="s">
+      <c r="A31" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="157"/>
       <c r="J31" s="102"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="171" t="s">
+      <c r="B32" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
+      <c r="C32" s="172"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
       <c r="H32" s="95"/>
       <c r="I32" s="95"/>
       <c r="J32" s="102"/>
@@ -10659,12 +11160,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="106"/>
-      <c r="B33" s="164"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="172"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
+      <c r="F33" s="165"/>
+      <c r="G33" s="173"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33"/>
@@ -10677,12 +11178,12 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="107"/>
-      <c r="B34" s="165"/>
-      <c r="C34" s="165"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="173"/>
+      <c r="B34" s="166"/>
+      <c r="C34" s="166"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="174"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="K34" s="102"/>
@@ -10694,12 +11195,12 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="108"/>
-      <c r="B35" s="166"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="174"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="167"/>
+      <c r="D35" s="167"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="167"/>
+      <c r="G35" s="175"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="95"/>
@@ -10752,64 +11253,64 @@
       <c r="P38" s="49"/>
     </row>
     <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="185" t="s">
+      <c r="A39" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="185" t="s">
+      <c r="B39" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="185" t="s">
+      <c r="D39" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="185" t="s">
+      <c r="E39" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="185" t="s">
+      <c r="F39" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G39" s="185" t="s">
+      <c r="G39" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H39" s="185" t="s">
+      <c r="H39" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="185" t="s">
+      <c r="I39" s="186" t="s">
         <v>229</v>
       </c>
-      <c r="J39" s="180" t="s">
+      <c r="J39" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K39" s="190" t="s">
+      <c r="K39" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L39" s="191"/>
-      <c r="M39" s="192" t="s">
+      <c r="L39" s="192"/>
+      <c r="M39" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N39" s="191"/>
+      <c r="N39" s="192"/>
       <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P39" s="185" t="s">
+      <c r="P39" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15">
-      <c r="A40" s="189"/>
-      <c r="B40" s="189"/>
+      <c r="A40" s="190"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="189"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="187"/>
+      <c r="D40" s="190"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="188"/>
       <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
@@ -10825,7 +11326,7 @@
       <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P40" s="189"/>
+      <c r="P40" s="190"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
@@ -11556,10 +12057,10 @@
         <v>167</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="158" t="s">
+      <c r="C15" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="158"/>
+      <c r="D15" s="159"/>
       <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
@@ -11569,10 +12070,10 @@
         <v>170</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="158" t="s">
+      <c r="C16" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="158"/>
+      <c r="D16" s="159"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="112" t="s">
@@ -11598,28 +12099,28 @@
       <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="134" t="s">
+      <c r="B20" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="95"/>
       <c r="I20" s="95"/>
       <c r="K20" s="95"/>
@@ -11631,12 +12132,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="106"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="164"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -11648,12 +12149,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="107"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="165"/>
-      <c r="F22" s="165"/>
-      <c r="G22" s="165"/>
+      <c r="B22" s="166"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="K22" s="102"/>
@@ -11665,12 +12166,12 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="108"/>
-      <c r="B23" s="166"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
+      <c r="B23" s="167"/>
+      <c r="C23" s="167"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="102"/>
       <c r="I23" s="102"/>
       <c r="J23" s="95"/>
@@ -11686,29 +12187,29 @@
       <c r="J24" s="102"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="153"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="157"/>
       <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="102"/>
@@ -11723,14 +12224,14 @@
       <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B27" s="137" t="s">
+      <c r="B27" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -11742,12 +12243,12 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="107"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="K28" s="102"/>
@@ -11759,12 +12260,12 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="108"/>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="95"/>
@@ -11793,29 +12294,29 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="151" t="s">
+      <c r="A31" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="157"/>
       <c r="J31" s="102"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="171" t="s">
+      <c r="B32" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
+      <c r="C32" s="172"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
       <c r="H32" s="95"/>
       <c r="I32" s="95"/>
       <c r="J32" s="102"/>
@@ -11828,12 +12329,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="106"/>
-      <c r="B33" s="164"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="172"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
+      <c r="F33" s="165"/>
+      <c r="G33" s="173"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33"/>
@@ -11846,12 +12347,12 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="107"/>
-      <c r="B34" s="165"/>
-      <c r="C34" s="165"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="173"/>
+      <c r="B34" s="166"/>
+      <c r="C34" s="166"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="174"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="K34" s="102"/>
@@ -11863,12 +12364,12 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="108"/>
-      <c r="B35" s="166"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="174"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="167"/>
+      <c r="D35" s="167"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="167"/>
+      <c r="G35" s="175"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="95"/>
@@ -11921,64 +12422,64 @@
       <c r="P38" s="49"/>
     </row>
     <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="185" t="s">
+      <c r="A39" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="185" t="s">
+      <c r="B39" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="185" t="s">
+      <c r="D39" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="185" t="s">
+      <c r="E39" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="185" t="s">
+      <c r="F39" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G39" s="185" t="s">
+      <c r="G39" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H39" s="194" t="s">
+      <c r="H39" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="194" t="s">
+      <c r="I39" s="195" t="s">
         <v>224</v>
       </c>
-      <c r="J39" s="180" t="s">
+      <c r="J39" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K39" s="190" t="s">
+      <c r="K39" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L39" s="191"/>
-      <c r="M39" s="192" t="s">
+      <c r="L39" s="192"/>
+      <c r="M39" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N39" s="191"/>
+      <c r="N39" s="192"/>
       <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P39" s="185" t="s">
+      <c r="P39" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15">
-      <c r="A40" s="189"/>
-      <c r="B40" s="189"/>
+      <c r="A40" s="190"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="189"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="187"/>
+      <c r="D40" s="190"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="188"/>
       <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
@@ -11994,7 +12495,7 @@
       <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P40" s="189"/>
+      <c r="P40" s="190"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
@@ -12695,10 +13196,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="158" t="s">
+      <c r="C17" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="158"/>
+      <c r="D17" s="159"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -12708,20 +13209,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="158"/>
+      <c r="D18" s="159"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="157" t="s">
+      <c r="C19" s="158" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="158"/>
+      <c r="D19" s="159"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="112" t="s">
@@ -12805,15 +13306,15 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="154" t="s">
+      <c r="A24" s="134" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="155"/>
-      <c r="C24" s="155"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="155"/>
-      <c r="G24" s="156"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="91" t="s">
@@ -12861,28 +13362,28 @@
       <c r="C28"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="133" t="s">
+      <c r="A29" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="137"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="136"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="95"/>
@@ -12900,12 +13401,12 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="106"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="164"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="165"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31" s="102"/>
@@ -12923,12 +13424,12 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="107"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="165"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="166"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -12946,12 +13447,12 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="108"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="166"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="167"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -12971,28 +13472,28 @@
       <c r="C34"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="151" t="s">
+      <c r="A35" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="153"/>
+      <c r="B35" s="156"/>
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="157"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="171" t="s">
+      <c r="B36" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
+      <c r="C36" s="172"/>
+      <c r="D36" s="172"/>
+      <c r="E36" s="172"/>
+      <c r="F36" s="172"/>
+      <c r="G36" s="172"/>
       <c r="H36" s="95"/>
       <c r="I36" s="95"/>
       <c r="J36" s="95"/>
@@ -13012,14 +13513,14 @@
       <c r="A37" s="106">
         <v>1</v>
       </c>
-      <c r="B37" s="137" t="s">
+      <c r="B37" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="137"/>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="137"/>
-      <c r="G37" s="137"/>
+      <c r="C37" s="141"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="141"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
       <c r="H37" s="102"/>
       <c r="I37" s="102"/>
       <c r="J37" s="102"/>
@@ -13037,12 +13538,12 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="107"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
+      <c r="B38" s="142"/>
+      <c r="C38" s="142"/>
+      <c r="D38" s="142"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -13060,12 +13561,12 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="108"/>
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
+      <c r="B39" s="143"/>
+      <c r="C39" s="143"/>
+      <c r="D39" s="143"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="143"/>
+      <c r="G39" s="143"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -13104,28 +13605,28 @@
       <c r="T40"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="151" t="s">
+      <c r="A41" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="152"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="152"/>
-      <c r="G41" s="153"/>
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="157"/>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="171" t="s">
+      <c r="B42" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="171"/>
-      <c r="D42" s="171"/>
-      <c r="E42" s="171"/>
-      <c r="F42" s="171"/>
-      <c r="G42" s="171"/>
+      <c r="C42" s="172"/>
+      <c r="D42" s="172"/>
+      <c r="E42" s="172"/>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
       <c r="H42" s="95"/>
       <c r="I42" s="95"/>
       <c r="J42" s="95"/>
@@ -13143,12 +13644,12 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="106"/>
-      <c r="B43" s="164"/>
-      <c r="C43" s="164"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="172"/>
+      <c r="B43" s="165"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="165"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="165"/>
+      <c r="G43" s="173"/>
       <c r="H43" s="102"/>
       <c r="I43" s="102"/>
       <c r="J43" s="102"/>
@@ -13166,12 +13667,12 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="107"/>
-      <c r="B44" s="165"/>
-      <c r="C44" s="165"/>
-      <c r="D44" s="165"/>
-      <c r="E44" s="165"/>
-      <c r="F44" s="165"/>
-      <c r="G44" s="173"/>
+      <c r="B44" s="166"/>
+      <c r="C44" s="166"/>
+      <c r="D44" s="166"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="166"/>
+      <c r="G44" s="174"/>
       <c r="H44" s="102"/>
       <c r="I44" s="102"/>
       <c r="J44" s="102"/>
@@ -13189,12 +13690,12 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="108"/>
-      <c r="B45" s="166"/>
-      <c r="C45" s="166"/>
-      <c r="D45" s="166"/>
-      <c r="E45" s="166"/>
-      <c r="F45" s="166"/>
-      <c r="G45" s="174"/>
+      <c r="B45" s="167"/>
+      <c r="C45" s="167"/>
+      <c r="D45" s="167"/>
+      <c r="E45" s="167"/>
+      <c r="F45" s="167"/>
+      <c r="G45" s="175"/>
       <c r="H45" s="102"/>
       <c r="I45" s="102"/>
       <c r="J45" s="102"/>
@@ -13264,82 +13765,82 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21">
-      <c r="A49" s="180" t="s">
+      <c r="A49" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B49" s="180" t="s">
+      <c r="B49" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="182" t="s">
+      <c r="C49" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="D49" s="180" t="s">
+      <c r="D49" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="185" t="s">
+      <c r="E49" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="185" t="s">
+      <c r="F49" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G49" s="180" t="s">
+      <c r="G49" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="180" t="s">
+      <c r="H49" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="I49" s="180" t="s">
+      <c r="I49" s="181" t="s">
         <v>236</v>
       </c>
-      <c r="J49" s="185" t="s">
+      <c r="J49" s="186" t="s">
         <v>237</v>
       </c>
-      <c r="K49" s="185" t="s">
+      <c r="K49" s="186" t="s">
         <v>207</v>
       </c>
-      <c r="L49" s="188" t="s">
+      <c r="L49" s="189" t="s">
         <v>224</v>
       </c>
-      <c r="M49" s="180" t="s">
+      <c r="M49" s="181" t="s">
         <v>224</v>
       </c>
-      <c r="N49" s="180" t="s">
+      <c r="N49" s="181" t="s">
         <v>221</v>
       </c>
-      <c r="O49" s="180" t="s">
+      <c r="O49" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="P49" s="183" t="s">
+      <c r="P49" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="Q49" s="184"/>
-      <c r="R49" s="183" t="s">
+      <c r="Q49" s="185"/>
+      <c r="R49" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="S49" s="184"/>
+      <c r="S49" s="185"/>
       <c r="T49" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="U49" s="180" t="s">
+      <c r="U49" s="181" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:21">
-      <c r="A50" s="181"/>
-      <c r="B50" s="181"/>
-      <c r="C50" s="181"/>
-      <c r="D50" s="181"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="181"/>
-      <c r="H50" s="181"/>
-      <c r="I50" s="181"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="187"/>
-      <c r="M50" s="181"/>
-      <c r="N50" s="181"/>
-      <c r="O50" s="187"/>
+      <c r="A50" s="182"/>
+      <c r="B50" s="182"/>
+      <c r="C50" s="182"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="187"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="182"/>
+      <c r="H50" s="182"/>
+      <c r="I50" s="182"/>
+      <c r="J50" s="187"/>
+      <c r="K50" s="187"/>
+      <c r="L50" s="188"/>
+      <c r="M50" s="182"/>
+      <c r="N50" s="182"/>
+      <c r="O50" s="188"/>
       <c r="P50" s="27" t="s">
         <v>74</v>
       </c>
@@ -13355,7 +13856,7 @@
       <c r="T50" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U50" s="181"/>
+      <c r="U50" s="182"/>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="7">
@@ -14223,10 +14724,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="158" t="s">
+      <c r="C13" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="158"/>
+      <c r="D13" s="159"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -14236,10 +14737,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="158" t="s">
+      <c r="C14" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="158"/>
+      <c r="D14" s="159"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -14265,28 +14766,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="140"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -14298,12 +14799,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -14315,12 +14816,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="165"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
+      <c r="B20" s="166"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="166"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -14332,12 +14833,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="166"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
+      <c r="B21" s="167"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -14353,29 +14854,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="151" t="s">
+      <c r="A23" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="153"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="172"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -14390,14 +14891,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -14409,12 +14910,12 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="107"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
+      <c r="B26" s="142"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -14426,12 +14927,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
+      <c r="B27" s="143"/>
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -14460,29 +14961,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="151" t="s">
+      <c r="A29" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="152"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="153"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="157"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="171" t="s">
+      <c r="B30" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="172"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -14495,12 +14996,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="172"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="173"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -14513,12 +15014,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="173"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="174"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -14530,12 +15031,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="174"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="175"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -14588,64 +15089,64 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="185" t="s">
+      <c r="A37" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="185" t="s">
+      <c r="B37" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="185" t="s">
+      <c r="D37" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="185" t="s">
+      <c r="E37" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="185" t="s">
+      <c r="F37" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="185" t="s">
+      <c r="G37" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="185" t="s">
+      <c r="H37" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="185" t="s">
+      <c r="I37" s="186" t="s">
         <v>229</v>
       </c>
-      <c r="J37" s="180" t="s">
+      <c r="J37" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="190" t="s">
+      <c r="K37" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L37" s="191"/>
-      <c r="M37" s="192" t="s">
+      <c r="L37" s="192"/>
+      <c r="M37" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N37" s="191"/>
+      <c r="N37" s="192"/>
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="185" t="s">
+      <c r="P37" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="189"/>
-      <c r="B38" s="189"/>
+      <c r="A38" s="190"/>
+      <c r="B38" s="190"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="189"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="187"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="188"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -14661,7 +15162,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="189"/>
+      <c r="P38" s="190"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
@@ -15392,10 +15893,10 @@
         <v>167</v>
       </c>
       <c r="B15" s="111"/>
-      <c r="C15" s="158" t="s">
+      <c r="C15" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="158"/>
+      <c r="D15" s="159"/>
       <c r="E15" s="1" t="s">
         <v>169</v>
       </c>
@@ -15405,10 +15906,10 @@
         <v>170</v>
       </c>
       <c r="B16" s="111"/>
-      <c r="C16" s="158" t="s">
+      <c r="C16" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="158"/>
+      <c r="D16" s="159"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="112" t="s">
@@ -15434,28 +15935,28 @@
       <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="134" t="s">
+      <c r="B20" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C20" s="135"/>
-      <c r="D20" s="135"/>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="136"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="140"/>
       <c r="H20" s="95"/>
       <c r="I20" s="95"/>
       <c r="K20" s="95"/>
@@ -15467,12 +15968,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="106"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="164"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="K21" s="102"/>
@@ -15484,12 +15985,12 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="107"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="165"/>
-      <c r="E22" s="165"/>
-      <c r="F22" s="165"/>
-      <c r="G22" s="165"/>
+      <c r="B22" s="166"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="166"/>
+      <c r="F22" s="166"/>
+      <c r="G22" s="166"/>
       <c r="H22" s="102"/>
       <c r="I22" s="102"/>
       <c r="K22" s="102"/>
@@ -15501,12 +16002,12 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="108"/>
-      <c r="B23" s="166"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="166"/>
-      <c r="F23" s="166"/>
-      <c r="G23" s="166"/>
+      <c r="B23" s="167"/>
+      <c r="C23" s="167"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="167"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="102"/>
       <c r="I23" s="102"/>
       <c r="J23" s="95"/>
@@ -15522,29 +16023,29 @@
       <c r="J24" s="102"/>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="151" t="s">
+      <c r="A25" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="153"/>
+      <c r="B25" s="156"/>
+      <c r="C25" s="156"/>
+      <c r="D25" s="156"/>
+      <c r="E25" s="156"/>
+      <c r="F25" s="156"/>
+      <c r="G25" s="157"/>
       <c r="J25" s="102"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="171" t="s">
+      <c r="B26" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="171"/>
-      <c r="D26" s="171"/>
-      <c r="E26" s="171"/>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
       <c r="H26" s="95"/>
       <c r="I26" s="95"/>
       <c r="J26" s="102"/>
@@ -15559,14 +16060,14 @@
       <c r="A27" s="106">
         <v>1</v>
       </c>
-      <c r="B27" s="137" t="s">
+      <c r="B27" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="K27" s="102"/>
@@ -15578,12 +16079,12 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="107"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
+      <c r="B28" s="142"/>
+      <c r="C28" s="142"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="142"/>
       <c r="H28" s="102"/>
       <c r="I28" s="102"/>
       <c r="K28" s="102"/>
@@ -15595,12 +16096,12 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="108"/>
-      <c r="B29" s="139"/>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-      <c r="G29" s="139"/>
+      <c r="B29" s="143"/>
+      <c r="C29" s="143"/>
+      <c r="D29" s="143"/>
+      <c r="E29" s="143"/>
+      <c r="F29" s="143"/>
+      <c r="G29" s="143"/>
       <c r="H29" s="102"/>
       <c r="I29" s="102"/>
       <c r="J29" s="95"/>
@@ -15629,29 +16130,29 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="151" t="s">
+      <c r="A31" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="152"/>
-      <c r="G31" s="153"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="157"/>
       <c r="J31" s="102"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B32" s="171" t="s">
+      <c r="B32" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C32" s="171"/>
-      <c r="D32" s="171"/>
-      <c r="E32" s="171"/>
-      <c r="F32" s="171"/>
-      <c r="G32" s="171"/>
+      <c r="C32" s="172"/>
+      <c r="D32" s="172"/>
+      <c r="E32" s="172"/>
+      <c r="F32" s="172"/>
+      <c r="G32" s="172"/>
       <c r="H32" s="95"/>
       <c r="I32" s="95"/>
       <c r="J32" s="102"/>
@@ -15664,12 +16165,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="106"/>
-      <c r="B33" s="164"/>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
-      <c r="G33" s="172"/>
+      <c r="B33" s="165"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
+      <c r="F33" s="165"/>
+      <c r="G33" s="173"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33"/>
@@ -15682,12 +16183,12 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="107"/>
-      <c r="B34" s="165"/>
-      <c r="C34" s="165"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="173"/>
+      <c r="B34" s="166"/>
+      <c r="C34" s="166"/>
+      <c r="D34" s="166"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="166"/>
+      <c r="G34" s="174"/>
       <c r="H34" s="102"/>
       <c r="I34" s="102"/>
       <c r="K34" s="102"/>
@@ -15699,12 +16200,12 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="108"/>
-      <c r="B35" s="166"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="166"/>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="174"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="167"/>
+      <c r="D35" s="167"/>
+      <c r="E35" s="167"/>
+      <c r="F35" s="167"/>
+      <c r="G35" s="175"/>
       <c r="H35" s="102"/>
       <c r="I35" s="102"/>
       <c r="J35" s="95"/>
@@ -15757,64 +16258,64 @@
       <c r="P38" s="49"/>
     </row>
     <row r="39" spans="1:17" ht="15">
-      <c r="A39" s="185" t="s">
+      <c r="A39" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="185" t="s">
+      <c r="B39" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C39" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D39" s="185" t="s">
+      <c r="D39" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="185" t="s">
+      <c r="E39" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="185" t="s">
+      <c r="F39" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G39" s="185" t="s">
+      <c r="G39" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H39" s="194" t="s">
+      <c r="H39" s="195" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="194" t="s">
+      <c r="I39" s="195" t="s">
         <v>224</v>
       </c>
-      <c r="J39" s="180" t="s">
+      <c r="J39" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K39" s="190" t="s">
+      <c r="K39" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L39" s="191"/>
-      <c r="M39" s="192" t="s">
+      <c r="L39" s="192"/>
+      <c r="M39" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N39" s="191"/>
+      <c r="N39" s="192"/>
       <c r="O39" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P39" s="185" t="s">
+      <c r="P39" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="15">
-      <c r="A40" s="189"/>
-      <c r="B40" s="189"/>
+      <c r="A40" s="190"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D40" s="189"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186"/>
-      <c r="G40" s="189"/>
-      <c r="H40" s="189"/>
-      <c r="I40" s="189"/>
-      <c r="J40" s="187"/>
+      <c r="D40" s="190"/>
+      <c r="E40" s="187"/>
+      <c r="F40" s="187"/>
+      <c r="G40" s="190"/>
+      <c r="H40" s="190"/>
+      <c r="I40" s="190"/>
+      <c r="J40" s="188"/>
       <c r="K40" s="53" t="s">
         <v>123</v>
       </c>
@@ -15830,7 +16331,7 @@
       <c r="O40" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P40" s="189"/>
+      <c r="P40" s="190"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="55">
@@ -16531,10 +17032,10 @@
         <v>167</v>
       </c>
       <c r="B17" s="111"/>
-      <c r="C17" s="158" t="s">
+      <c r="C17" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="158"/>
+      <c r="D17" s="159"/>
       <c r="E17" s="1" t="s">
         <v>169</v>
       </c>
@@ -16544,20 +17045,20 @@
         <v>170</v>
       </c>
       <c r="B18" s="111"/>
-      <c r="C18" s="158" t="s">
+      <c r="C18" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="158"/>
+      <c r="D18" s="159"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="111" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="111"/>
-      <c r="C19" s="157" t="s">
+      <c r="C19" s="158" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="158"/>
+      <c r="D19" s="159"/>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="112" t="s">
@@ -16640,15 +17141,15 @@
       <c r="A23" s="6"/>
     </row>
     <row r="24" spans="1:22">
-      <c r="A24" s="154" t="s">
+      <c r="A24" s="134" t="s">
         <v>256</v>
       </c>
-      <c r="B24" s="155"/>
-      <c r="C24" s="155"/>
-      <c r="D24" s="155"/>
-      <c r="E24" s="155"/>
-      <c r="F24" s="155"/>
-      <c r="G24" s="156"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="91" t="s">
@@ -16692,28 +17193,28 @@
       <c r="C28"/>
     </row>
     <row r="29" spans="1:22">
-      <c r="A29" s="133" t="s">
+      <c r="A29" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="133"/>
-      <c r="C29" s="133"/>
-      <c r="D29" s="133"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="G29" s="133"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="137"/>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C30" s="135"/>
-      <c r="D30" s="135"/>
-      <c r="E30" s="135"/>
-      <c r="F30" s="135"/>
-      <c r="G30" s="136"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="140"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="95"/>
@@ -16731,12 +17232,12 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="106"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="164"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="165"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31" s="102"/>
@@ -16754,12 +17255,12 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="107"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="165"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="166"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="J32" s="102"/>
@@ -16777,12 +17278,12 @@
     </row>
     <row r="33" spans="1:22">
       <c r="A33" s="108"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="166"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="167"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="102"/>
@@ -16802,28 +17303,28 @@
       <c r="C34"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="151" t="s">
+      <c r="A35" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
-      <c r="F35" s="152"/>
-      <c r="G35" s="153"/>
+      <c r="B35" s="156"/>
+      <c r="C35" s="156"/>
+      <c r="D35" s="156"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="156"/>
+      <c r="G35" s="157"/>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="171" t="s">
+      <c r="B36" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C36" s="171"/>
-      <c r="D36" s="171"/>
-      <c r="E36" s="171"/>
-      <c r="F36" s="171"/>
-      <c r="G36" s="171"/>
+      <c r="C36" s="172"/>
+      <c r="D36" s="172"/>
+      <c r="E36" s="172"/>
+      <c r="F36" s="172"/>
+      <c r="G36" s="172"/>
       <c r="H36" s="95"/>
       <c r="I36" s="95"/>
       <c r="J36" s="95"/>
@@ -16843,14 +17344,14 @@
       <c r="A37" s="106">
         <v>1</v>
       </c>
-      <c r="B37" s="137" t="s">
+      <c r="B37" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C37" s="137"/>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="137"/>
-      <c r="G37" s="137"/>
+      <c r="C37" s="141"/>
+      <c r="D37" s="141"/>
+      <c r="E37" s="141"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="141"/>
       <c r="H37" s="102"/>
       <c r="I37" s="102"/>
       <c r="J37" s="102"/>
@@ -16868,12 +17369,12 @@
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="107"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
+      <c r="B38" s="142"/>
+      <c r="C38" s="142"/>
+      <c r="D38" s="142"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="142"/>
+      <c r="G38" s="142"/>
       <c r="H38" s="102"/>
       <c r="I38" s="102"/>
       <c r="J38" s="102"/>
@@ -16891,12 +17392,12 @@
     </row>
     <row r="39" spans="1:22">
       <c r="A39" s="108"/>
-      <c r="B39" s="139"/>
-      <c r="C39" s="139"/>
-      <c r="D39" s="139"/>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
+      <c r="B39" s="143"/>
+      <c r="C39" s="143"/>
+      <c r="D39" s="143"/>
+      <c r="E39" s="143"/>
+      <c r="F39" s="143"/>
+      <c r="G39" s="143"/>
       <c r="H39" s="102"/>
       <c r="I39" s="102"/>
       <c r="J39" s="102"/>
@@ -16935,28 +17436,28 @@
       <c r="T40"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="151" t="s">
+      <c r="A41" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B41" s="152"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
-      <c r="F41" s="152"/>
-      <c r="G41" s="153"/>
+      <c r="B41" s="156"/>
+      <c r="C41" s="156"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="156"/>
+      <c r="F41" s="156"/>
+      <c r="G41" s="157"/>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="171" t="s">
+      <c r="B42" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="171"/>
-      <c r="D42" s="171"/>
-      <c r="E42" s="171"/>
-      <c r="F42" s="171"/>
-      <c r="G42" s="171"/>
+      <c r="C42" s="172"/>
+      <c r="D42" s="172"/>
+      <c r="E42" s="172"/>
+      <c r="F42" s="172"/>
+      <c r="G42" s="172"/>
       <c r="H42" s="95"/>
       <c r="I42" s="95"/>
       <c r="J42" s="95"/>
@@ -16974,12 +17475,12 @@
     </row>
     <row r="43" spans="1:22">
       <c r="A43" s="106"/>
-      <c r="B43" s="164"/>
-      <c r="C43" s="164"/>
-      <c r="D43" s="164"/>
-      <c r="E43" s="164"/>
-      <c r="F43" s="164"/>
-      <c r="G43" s="172"/>
+      <c r="B43" s="165"/>
+      <c r="C43" s="165"/>
+      <c r="D43" s="165"/>
+      <c r="E43" s="165"/>
+      <c r="F43" s="165"/>
+      <c r="G43" s="173"/>
       <c r="H43" s="102"/>
       <c r="I43" s="102"/>
       <c r="J43" s="102"/>
@@ -16997,12 +17498,12 @@
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="107"/>
-      <c r="B44" s="165"/>
-      <c r="C44" s="165"/>
-      <c r="D44" s="165"/>
-      <c r="E44" s="165"/>
-      <c r="F44" s="165"/>
-      <c r="G44" s="173"/>
+      <c r="B44" s="166"/>
+      <c r="C44" s="166"/>
+      <c r="D44" s="166"/>
+      <c r="E44" s="166"/>
+      <c r="F44" s="166"/>
+      <c r="G44" s="174"/>
       <c r="H44" s="102"/>
       <c r="I44" s="102"/>
       <c r="J44" s="102"/>
@@ -17020,12 +17521,12 @@
     </row>
     <row r="45" spans="1:22">
       <c r="A45" s="108"/>
-      <c r="B45" s="166"/>
-      <c r="C45" s="166"/>
-      <c r="D45" s="166"/>
-      <c r="E45" s="166"/>
-      <c r="F45" s="166"/>
-      <c r="G45" s="174"/>
+      <c r="B45" s="167"/>
+      <c r="C45" s="167"/>
+      <c r="D45" s="167"/>
+      <c r="E45" s="167"/>
+      <c r="F45" s="167"/>
+      <c r="G45" s="175"/>
       <c r="H45" s="102"/>
       <c r="I45" s="102"/>
       <c r="J45" s="102"/>
@@ -17095,82 +17596,82 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21">
-      <c r="A49" s="180" t="s">
+      <c r="A49" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B49" s="180" t="s">
+      <c r="B49" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="182" t="s">
+      <c r="C49" s="183" t="s">
         <v>1</v>
       </c>
-      <c r="D49" s="180" t="s">
+      <c r="D49" s="181" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="185" t="s">
+      <c r="E49" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="185" t="s">
+      <c r="F49" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G49" s="180" t="s">
+      <c r="G49" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="H49" s="180" t="s">
+      <c r="H49" s="181" t="s">
         <v>113</v>
       </c>
-      <c r="I49" s="180" t="s">
+      <c r="I49" s="181" t="s">
         <v>236</v>
       </c>
-      <c r="J49" s="185" t="s">
+      <c r="J49" s="186" t="s">
         <v>237</v>
       </c>
-      <c r="K49" s="185" t="s">
+      <c r="K49" s="186" t="s">
         <v>207</v>
       </c>
-      <c r="L49" s="188" t="s">
+      <c r="L49" s="189" t="s">
         <v>224</v>
       </c>
-      <c r="M49" s="180" t="s">
+      <c r="M49" s="181" t="s">
         <v>224</v>
       </c>
-      <c r="N49" s="180" t="s">
+      <c r="N49" s="181" t="s">
         <v>221</v>
       </c>
-      <c r="O49" s="180" t="s">
+      <c r="O49" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="P49" s="183" t="s">
+      <c r="P49" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="Q49" s="184"/>
-      <c r="R49" s="183" t="s">
+      <c r="Q49" s="185"/>
+      <c r="R49" s="184" t="s">
         <v>16</v>
       </c>
-      <c r="S49" s="184"/>
+      <c r="S49" s="185"/>
       <c r="T49" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="U49" s="180" t="s">
+      <c r="U49" s="181" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:21">
-      <c r="A50" s="181"/>
-      <c r="B50" s="181"/>
-      <c r="C50" s="181"/>
-      <c r="D50" s="181"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186"/>
-      <c r="G50" s="181"/>
-      <c r="H50" s="181"/>
-      <c r="I50" s="181"/>
-      <c r="J50" s="186"/>
-      <c r="K50" s="186"/>
-      <c r="L50" s="187"/>
-      <c r="M50" s="181"/>
-      <c r="N50" s="181"/>
-      <c r="O50" s="187"/>
+      <c r="A50" s="182"/>
+      <c r="B50" s="182"/>
+      <c r="C50" s="182"/>
+      <c r="D50" s="182"/>
+      <c r="E50" s="187"/>
+      <c r="F50" s="187"/>
+      <c r="G50" s="182"/>
+      <c r="H50" s="182"/>
+      <c r="I50" s="182"/>
+      <c r="J50" s="187"/>
+      <c r="K50" s="187"/>
+      <c r="L50" s="188"/>
+      <c r="M50" s="182"/>
+      <c r="N50" s="182"/>
+      <c r="O50" s="188"/>
       <c r="P50" s="27" t="s">
         <v>74</v>
       </c>
@@ -17186,7 +17687,7 @@
       <c r="T50" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="U50" s="181"/>
+      <c r="U50" s="182"/>
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="7">
@@ -18062,10 +18563,10 @@
         <v>167</v>
       </c>
       <c r="B13" s="111"/>
-      <c r="C13" s="158" t="s">
+      <c r="C13" s="159" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="158"/>
+      <c r="D13" s="159"/>
       <c r="E13" s="1" t="s">
         <v>169</v>
       </c>
@@ -18075,10 +18576,10 @@
         <v>170</v>
       </c>
       <c r="B14" s="111"/>
-      <c r="C14" s="158" t="s">
+      <c r="C14" s="159" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="158"/>
+      <c r="D14" s="159"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="112" t="s">
@@ -18104,28 +18605,28 @@
       <c r="A16" s="6"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="133" t="s">
+      <c r="A17" s="137" t="s">
         <v>185</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="133"/>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="138" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="135"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="136"/>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="140"/>
       <c r="H18" s="95"/>
       <c r="I18" s="95"/>
       <c r="K18" s="95"/>
@@ -18137,12 +18638,12 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="106"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="164"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="164"/>
-      <c r="G19" s="164"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="165"/>
+      <c r="E19" s="165"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="165"/>
       <c r="H19" s="102"/>
       <c r="I19" s="102"/>
       <c r="K19" s="102"/>
@@ -18154,12 +18655,12 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="107"/>
-      <c r="B20" s="165"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
+      <c r="B20" s="166"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="166"/>
+      <c r="F20" s="166"/>
+      <c r="G20" s="166"/>
       <c r="H20" s="102"/>
       <c r="I20" s="102"/>
       <c r="K20" s="102"/>
@@ -18171,12 +18672,12 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="108"/>
-      <c r="B21" s="166"/>
-      <c r="C21" s="166"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="166"/>
-      <c r="F21" s="166"/>
-      <c r="G21" s="166"/>
+      <c r="B21" s="167"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="167"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="102"/>
       <c r="I21" s="102"/>
       <c r="J21" s="95"/>
@@ -18192,29 +18693,29 @@
       <c r="J22" s="102"/>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="151" t="s">
+      <c r="A23" s="155" t="s">
         <v>186</v>
       </c>
-      <c r="B23" s="152"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="152"/>
-      <c r="G23" s="153"/>
+      <c r="B23" s="156"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="157"/>
       <c r="J23" s="102"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="171" t="s">
+      <c r="B24" s="172" t="s">
         <v>177</v>
       </c>
-      <c r="C24" s="171"/>
-      <c r="D24" s="171"/>
-      <c r="E24" s="171"/>
-      <c r="F24" s="171"/>
-      <c r="G24" s="171"/>
+      <c r="C24" s="172"/>
+      <c r="D24" s="172"/>
+      <c r="E24" s="172"/>
+      <c r="F24" s="172"/>
+      <c r="G24" s="172"/>
       <c r="H24" s="95"/>
       <c r="I24" s="95"/>
       <c r="J24" s="102"/>
@@ -18229,14 +18730,14 @@
       <c r="A25" s="106">
         <v>1</v>
       </c>
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="141" t="s">
         <v>178</v>
       </c>
-      <c r="C25" s="137"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
-      <c r="G25" s="137"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
       <c r="H25" s="102"/>
       <c r="I25" s="102"/>
       <c r="K25" s="102"/>
@@ -18248,12 +18749,12 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="107"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
+      <c r="B26" s="142"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
       <c r="H26" s="102"/>
       <c r="I26" s="102"/>
       <c r="K26" s="102"/>
@@ -18265,12 +18766,12 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="108"/>
-      <c r="B27" s="139"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="139"/>
-      <c r="F27" s="139"/>
-      <c r="G27" s="139"/>
+      <c r="B27" s="143"/>
+      <c r="C27" s="143"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
       <c r="H27" s="102"/>
       <c r="I27" s="102"/>
       <c r="J27" s="95"/>
@@ -18299,29 +18800,29 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="151" t="s">
+      <c r="A29" s="155" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="152"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
-      <c r="F29" s="152"/>
-      <c r="G29" s="153"/>
+      <c r="B29" s="156"/>
+      <c r="C29" s="156"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="156"/>
+      <c r="G29" s="157"/>
       <c r="J29" s="102"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="105" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="171" t="s">
+      <c r="B30" s="172" t="s">
         <v>179</v>
       </c>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
+      <c r="C30" s="172"/>
+      <c r="D30" s="172"/>
+      <c r="E30" s="172"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="172"/>
       <c r="H30" s="95"/>
       <c r="I30" s="95"/>
       <c r="J30" s="102"/>
@@ -18334,12 +18835,12 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="106"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="164"/>
-      <c r="D31" s="164"/>
-      <c r="E31" s="164"/>
-      <c r="F31" s="164"/>
-      <c r="G31" s="172"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="165"/>
+      <c r="E31" s="165"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="173"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31"/>
@@ -18352,12 +18853,12 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="107"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="165"/>
-      <c r="G32" s="173"/>
+      <c r="B32" s="166"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="166"/>
+      <c r="F32" s="166"/>
+      <c r="G32" s="174"/>
       <c r="H32" s="102"/>
       <c r="I32" s="102"/>
       <c r="K32" s="102"/>
@@ -18369,12 +18870,12 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="108"/>
-      <c r="B33" s="166"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="166"/>
-      <c r="F33" s="166"/>
-      <c r="G33" s="174"/>
+      <c r="B33" s="167"/>
+      <c r="C33" s="167"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="167"/>
+      <c r="G33" s="175"/>
       <c r="H33" s="102"/>
       <c r="I33" s="102"/>
       <c r="J33" s="95"/>
@@ -18427,64 +18928,64 @@
       <c r="P36" s="49"/>
     </row>
     <row r="37" spans="1:17" ht="15">
-      <c r="A37" s="185" t="s">
+      <c r="A37" s="186" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="185" t="s">
+      <c r="B37" s="186" t="s">
         <v>116</v>
       </c>
       <c r="C37" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="185" t="s">
+      <c r="D37" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="185" t="s">
+      <c r="E37" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="F37" s="185" t="s">
+      <c r="F37" s="186" t="s">
         <v>170</v>
       </c>
-      <c r="G37" s="185" t="s">
+      <c r="G37" s="186" t="s">
         <v>136</v>
       </c>
-      <c r="H37" s="185" t="s">
+      <c r="H37" s="186" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="185" t="s">
+      <c r="I37" s="186" t="s">
         <v>229</v>
       </c>
-      <c r="J37" s="180" t="s">
+      <c r="J37" s="181" t="s">
         <v>189</v>
       </c>
-      <c r="K37" s="190" t="s">
+      <c r="K37" s="191" t="s">
         <v>119</v>
       </c>
-      <c r="L37" s="191"/>
-      <c r="M37" s="192" t="s">
+      <c r="L37" s="192"/>
+      <c r="M37" s="193" t="s">
         <v>120</v>
       </c>
-      <c r="N37" s="191"/>
+      <c r="N37" s="192"/>
       <c r="O37" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="P37" s="185" t="s">
+      <c r="P37" s="186" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="15">
-      <c r="A38" s="189"/>
-      <c r="B38" s="189"/>
+      <c r="A38" s="190"/>
+      <c r="B38" s="190"/>
       <c r="C38" s="52" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="189"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186"/>
-      <c r="G38" s="189"/>
-      <c r="H38" s="189"/>
-      <c r="I38" s="189"/>
-      <c r="J38" s="187"/>
+      <c r="D38" s="190"/>
+      <c r="E38" s="187"/>
+      <c r="F38" s="187"/>
+      <c r="G38" s="190"/>
+      <c r="H38" s="190"/>
+      <c r="I38" s="190"/>
+      <c r="J38" s="188"/>
       <c r="K38" s="53" t="s">
         <v>123</v>
       </c>
@@ -18500,7 +19001,7 @@
       <c r="O38" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="P38" s="189"/>
+      <c r="P38" s="190"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="55">
